--- a/data/interim/itu_mobile_subs_processed.xlsx
+++ b/data/interim/itu_mobile_subs_processed.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,37 +417,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>mobile_subs</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mobile_subs</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>series_code</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>series_units</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>data_source</t>
         </is>
@@ -475,7 +463,7 @@
         <v>2010</v>
       </c>
       <c r="C2" t="n">
-        <v>3865350</v>
+        <v>3865354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -508,7 +496,7 @@
         <v>2011</v>
       </c>
       <c r="C3" t="n">
-        <v>3211220</v>
+        <v>3211215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -541,7 +529,7 @@
         <v>2012</v>
       </c>
       <c r="C4" t="n">
-        <v>3322840</v>
+        <v>3322837</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -574,7 +562,7 @@
         <v>2013</v>
       </c>
       <c r="C5" t="n">
-        <v>3346280</v>
+        <v>3346275</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -607,7 +595,7 @@
         <v>2014</v>
       </c>
       <c r="C6" t="n">
-        <v>3459140</v>
+        <v>3459137</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -673,7 +661,7 @@
         <v>2016</v>
       </c>
       <c r="C8" t="n">
-        <v>3434570</v>
+        <v>3434567</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -706,7 +694,7 @@
         <v>2017</v>
       </c>
       <c r="C9" t="n">
-        <v>3488520</v>
+        <v>3488524</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -739,7 +727,7 @@
         <v>2018</v>
       </c>
       <c r="C10" t="n">
-        <v>3579260</v>
+        <v>3579257</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -772,7 +760,7 @@
         <v>2019</v>
       </c>
       <c r="C11" t="n">
-        <v>3618750</v>
+        <v>3618747</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -805,7 +793,7 @@
         <v>2020</v>
       </c>
       <c r="C12" t="n">
-        <v>3488800</v>
+        <v>3488797</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -838,7 +826,7 @@
         <v>2021</v>
       </c>
       <c r="C13" t="n">
-        <v>3599280</v>
+        <v>3599278</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -871,7 +859,7 @@
         <v>2022</v>
       </c>
       <c r="C14" t="n">
-        <v>3760700</v>
+        <v>3760695</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -904,7 +892,7 @@
         <v>2023</v>
       </c>
       <c r="C15" t="n">
-        <v>3959450</v>
+        <v>3959451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -937,7 +925,7 @@
         <v>2024</v>
       </c>
       <c r="C16" t="n">
-        <v>4011320</v>
+        <v>4011322</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1003,7 +991,7 @@
         <v>2011</v>
       </c>
       <c r="C18" t="n">
-        <v>13022600</v>
+        <v>13022578</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1102,7 +1090,7 @@
         <v>2014</v>
       </c>
       <c r="C21" t="n">
-        <v>12952600</v>
+        <v>12952605</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1135,7 +1123,7 @@
         <v>2015</v>
       </c>
       <c r="C22" t="n">
-        <v>13470600</v>
+        <v>13470623</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1168,7 +1156,7 @@
         <v>2016</v>
       </c>
       <c r="C23" t="n">
-        <v>11079500</v>
+        <v>11079460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1300,7 +1288,7 @@
         <v>2020</v>
       </c>
       <c r="C27" t="n">
-        <v>10717400</v>
+        <v>10717445</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1333,7 +1321,7 @@
         <v>2021</v>
       </c>
       <c r="C28" t="n">
-        <v>10882200</v>
+        <v>10882217</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1366,7 +1354,7 @@
         <v>2022</v>
       </c>
       <c r="C29" t="n">
-        <v>10983300</v>
+        <v>10983348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1399,7 +1387,7 @@
         <v>2023</v>
       </c>
       <c r="C30" t="n">
-        <v>11116000</v>
+        <v>11115951</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1465,7 +1453,7 @@
         <v>2010</v>
       </c>
       <c r="C32" t="n">
-        <v>9100110</v>
+        <v>9100113</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1498,7 +1486,7 @@
         <v>2011</v>
       </c>
       <c r="C33" t="n">
-        <v>10120100</v>
+        <v>10120105</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1564,7 +1552,7 @@
         <v>2013</v>
       </c>
       <c r="C35" t="n">
-        <v>10130100</v>
+        <v>10130102</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1597,7 +1585,7 @@
         <v>2014</v>
       </c>
       <c r="C36" t="n">
-        <v>10552500</v>
+        <v>10552520</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1630,7 +1618,7 @@
         <v>2015</v>
       </c>
       <c r="C37" t="n">
-        <v>10697100</v>
+        <v>10697132</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1828,7 +1816,7 @@
         <v>2021</v>
       </c>
       <c r="C43" t="n">
-        <v>10817100</v>
+        <v>10817071</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1894,7 +1882,7 @@
         <v>2023</v>
       </c>
       <c r="C45" t="n">
-        <v>11111300</v>
+        <v>11111340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1927,7 +1915,7 @@
         <v>2024</v>
       </c>
       <c r="C46" t="n">
-        <v>11323000</v>
+        <v>11323012</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1960,7 +1948,7 @@
         <v>2010</v>
       </c>
       <c r="C47" t="n">
-        <v>12154000</v>
+        <v>12154041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1993,7 +1981,7 @@
         <v>2011</v>
       </c>
       <c r="C48" t="n">
-        <v>12495900</v>
+        <v>12495934</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2026,7 +2014,7 @@
         <v>2012</v>
       </c>
       <c r="C49" t="n">
-        <v>12313400</v>
+        <v>12313375</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2059,7 +2047,7 @@
         <v>2013</v>
       </c>
       <c r="C50" t="n">
-        <v>12315200</v>
+        <v>12315217</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2092,7 +2080,7 @@
         <v>2014</v>
       </c>
       <c r="C51" t="n">
-        <v>12734700</v>
+        <v>12734724</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2125,7 +2113,7 @@
         <v>2015</v>
       </c>
       <c r="C52" t="n">
-        <v>12774100</v>
+        <v>12774090</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2158,7 +2146,7 @@
         <v>2016</v>
       </c>
       <c r="C53" t="n">
-        <v>12550800</v>
+        <v>12550821</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2191,7 +2179,7 @@
         <v>2017</v>
       </c>
       <c r="C54" t="n">
-        <v>11357300</v>
+        <v>11357286</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2224,7 +2212,7 @@
         <v>2018</v>
       </c>
       <c r="C55" t="n">
-        <v>11447400</v>
+        <v>11447351</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2257,7 +2245,7 @@
         <v>2019</v>
       </c>
       <c r="C56" t="n">
-        <v>11509600</v>
+        <v>11509573</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2290,7 +2278,7 @@
         <v>2020</v>
       </c>
       <c r="C57" t="n">
-        <v>11529700</v>
+        <v>11529728</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2323,7 +2311,7 @@
         <v>2021</v>
       </c>
       <c r="C58" t="n">
-        <v>11740100</v>
+        <v>11740118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2356,7 +2344,7 @@
         <v>2022</v>
       </c>
       <c r="C59" t="n">
-        <v>11837400</v>
+        <v>11837444</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2389,7 +2377,7 @@
         <v>2023</v>
       </c>
       <c r="C60" t="n">
-        <v>12087300</v>
+        <v>12087287</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2422,7 +2410,7 @@
         <v>2024</v>
       </c>
       <c r="C61" t="n">
-        <v>12197100</v>
+        <v>12197121</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2521,7 +2509,7 @@
         <v>2012</v>
       </c>
       <c r="C64" t="n">
-        <v>10676500</v>
+        <v>10676471</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2554,7 +2542,7 @@
         <v>2013</v>
       </c>
       <c r="C65" t="n">
-        <v>11114400</v>
+        <v>11114440</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2587,7 +2575,7 @@
         <v>2014</v>
       </c>
       <c r="C66" t="n">
-        <v>11401900</v>
+        <v>11401927</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2620,7 +2608,7 @@
         <v>2015</v>
       </c>
       <c r="C67" t="n">
-        <v>11448300</v>
+        <v>11448281</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2653,7 +2641,7 @@
         <v>2016</v>
       </c>
       <c r="C68" t="n">
-        <v>11439900</v>
+        <v>11439866</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2686,7 +2674,7 @@
         <v>2017</v>
       </c>
       <c r="C69" t="n">
-        <v>11415100</v>
+        <v>11415141</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2719,7 +2707,7 @@
         <v>2018</v>
       </c>
       <c r="C70" t="n">
-        <v>11619700</v>
+        <v>11619651</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2752,7 +2740,7 @@
         <v>2019</v>
       </c>
       <c r="C71" t="n">
-        <v>11627200</v>
+        <v>11627249</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -2785,7 +2773,7 @@
         <v>2020</v>
       </c>
       <c r="C72" t="n">
-        <v>11704100</v>
+        <v>11704084</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -2818,7 +2806,7 @@
         <v>2021</v>
       </c>
       <c r="C73" t="n">
-        <v>11760100</v>
+        <v>11760087</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -2851,7 +2839,7 @@
         <v>2022</v>
       </c>
       <c r="C74" t="n">
-        <v>11770600</v>
+        <v>11770639</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2884,7 +2872,7 @@
         <v>2023</v>
       </c>
       <c r="C75" t="n">
-        <v>11757300</v>
+        <v>11757329</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2917,7 +2905,7 @@
         <v>2024</v>
       </c>
       <c r="C76" t="n">
-        <v>11875400</v>
+        <v>11875413</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2950,7 +2938,7 @@
         <v>2010</v>
       </c>
       <c r="C77" t="n">
-        <v>10199900</v>
+        <v>10199942</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -2983,7 +2971,7 @@
         <v>2011</v>
       </c>
       <c r="C78" t="n">
-        <v>10475100</v>
+        <v>10475083</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3016,7 +3004,7 @@
         <v>2012</v>
       </c>
       <c r="C79" t="n">
-        <v>10780700</v>
+        <v>10780732</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -3049,7 +3037,7 @@
         <v>2013</v>
       </c>
       <c r="C80" t="n">
-        <v>10486800</v>
+        <v>10486824</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -3082,7 +3070,7 @@
         <v>2014</v>
       </c>
       <c r="C81" t="n">
-        <v>9486930</v>
+        <v>9486927</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -3115,7 +3103,7 @@
         <v>2015</v>
       </c>
       <c r="C82" t="n">
-        <v>9194630</v>
+        <v>9194633</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -3148,7 +3136,7 @@
         <v>2016</v>
       </c>
       <c r="C83" t="n">
-        <v>8973870</v>
+        <v>8973869</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -3181,7 +3169,7 @@
         <v>2017</v>
       </c>
       <c r="C84" t="n">
-        <v>8532910</v>
+        <v>8532908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -3247,7 +3235,7 @@
         <v>2019</v>
       </c>
       <c r="C86" t="n">
-        <v>8134580</v>
+        <v>8134581</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -3280,7 +3268,7 @@
         <v>2020</v>
       </c>
       <c r="C87" t="n">
-        <v>7945740</v>
+        <v>7945739</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -3313,7 +3301,7 @@
         <v>2021</v>
       </c>
       <c r="C88" t="n">
-        <v>7902760</v>
+        <v>7902756</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -3346,7 +3334,7 @@
         <v>2022</v>
       </c>
       <c r="C89" t="n">
-        <v>7964360</v>
+        <v>7964361</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -3379,7 +3367,7 @@
         <v>2023</v>
       </c>
       <c r="C90" t="n">
-        <v>8014470</v>
+        <v>8014473</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -3412,7 +3400,7 @@
         <v>2024</v>
       </c>
       <c r="C91" t="n">
-        <v>7978610</v>
+        <v>7978611</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -3445,7 +3433,7 @@
         <v>2010</v>
       </c>
       <c r="C92" t="n">
-        <v>1034070</v>
+        <v>1034071</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -3478,7 +3466,7 @@
         <v>2011</v>
       </c>
       <c r="C93" t="n">
-        <v>1090940</v>
+        <v>1090944</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -3511,7 +3499,7 @@
         <v>2012</v>
       </c>
       <c r="C94" t="n">
-        <v>1110940</v>
+        <v>1110935</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -3544,7 +3532,7 @@
         <v>2013</v>
       </c>
       <c r="C95" t="n">
-        <v>1099620</v>
+        <v>1099621</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -3577,7 +3565,7 @@
         <v>2014</v>
       </c>
       <c r="C96" t="n">
-        <v>1110800</v>
+        <v>1110802</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -3610,7 +3598,7 @@
         <v>2015</v>
       </c>
       <c r="C97" t="n">
-        <v>1111120</v>
+        <v>1111123</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -3676,7 +3664,7 @@
         <v>2017</v>
       </c>
       <c r="C99" t="n">
-        <v>1176800</v>
+        <v>1176801</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -3709,7 +3697,7 @@
         <v>2018</v>
       </c>
       <c r="C100" t="n">
-        <v>1200380</v>
+        <v>1200378</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -3742,7 +3730,7 @@
         <v>2019</v>
       </c>
       <c r="C101" t="n">
-        <v>1243150</v>
+        <v>1243151</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -3808,7 +3796,7 @@
         <v>2021</v>
       </c>
       <c r="C103" t="n">
-        <v>1320790</v>
+        <v>1320794</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -3874,7 +3862,7 @@
         <v>2023</v>
       </c>
       <c r="C105" t="n">
-        <v>1433500</v>
+        <v>1433497</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -3907,7 +3895,7 @@
         <v>2024</v>
       </c>
       <c r="C106" t="n">
-        <v>1509690</v>
+        <v>1509691</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -4468,7 +4456,7 @@
         <v>2011</v>
       </c>
       <c r="C123" t="n">
-        <v>7173190</v>
+        <v>7173185</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -4501,7 +4489,7 @@
         <v>2012</v>
       </c>
       <c r="C124" t="n">
-        <v>7292760</v>
+        <v>7292756</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -4534,7 +4522,7 @@
         <v>2013</v>
       </c>
       <c r="C125" t="n">
-        <v>7031150</v>
+        <v>7031152</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -4567,7 +4555,7 @@
         <v>2014</v>
       </c>
       <c r="C126" t="n">
-        <v>7160230</v>
+        <v>7160233</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -4600,7 +4588,7 @@
         <v>2015</v>
       </c>
       <c r="C127" t="n">
-        <v>7079250</v>
+        <v>7079249</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -4633,7 +4621,7 @@
         <v>2016</v>
       </c>
       <c r="C128" t="n">
-        <v>6985040</v>
+        <v>6985035</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -4666,7 +4654,7 @@
         <v>2017</v>
       </c>
       <c r="C129" t="n">
-        <v>7140860</v>
+        <v>7140859</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -4699,7 +4687,7 @@
         <v>2018</v>
       </c>
       <c r="C130" t="n">
-        <v>7216220</v>
+        <v>7216215</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -4732,7 +4720,7 @@
         <v>2019</v>
       </c>
       <c r="C131" t="n">
-        <v>7243470</v>
+        <v>7243465</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -4765,7 +4753,7 @@
         <v>2020</v>
       </c>
       <c r="C132" t="n">
-        <v>7252680</v>
+        <v>7252675</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -4798,7 +4786,7 @@
         <v>2021</v>
       </c>
       <c r="C133" t="n">
-        <v>7356350</v>
+        <v>7356353</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -4831,7 +4819,7 @@
         <v>2022</v>
       </c>
       <c r="C134" t="n">
-        <v>7466200</v>
+        <v>7466202</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -4864,7 +4852,7 @@
         <v>2023</v>
       </c>
       <c r="C135" t="n">
-        <v>7537310</v>
+        <v>7537305</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -4897,7 +4885,7 @@
         <v>2024</v>
       </c>
       <c r="C136" t="n">
-        <v>7572580</v>
+        <v>7572576</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -4930,7 +4918,7 @@
         <v>2010</v>
       </c>
       <c r="C137" t="n">
-        <v>51389400</v>
+        <v>51389417</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -4963,7 +4951,7 @@
         <v>2011</v>
       </c>
       <c r="C138" t="n">
-        <v>52590500</v>
+        <v>52590507</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -4996,7 +4984,7 @@
         <v>2012</v>
       </c>
       <c r="C139" t="n">
-        <v>50665100</v>
+        <v>50665099</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -5029,7 +5017,7 @@
         <v>2013</v>
       </c>
       <c r="C140" t="n">
-        <v>50158700</v>
+        <v>50158689</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -5062,7 +5050,7 @@
         <v>2014</v>
       </c>
       <c r="C141" t="n">
-        <v>50806300</v>
+        <v>50806251</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -5095,7 +5083,7 @@
         <v>2015</v>
       </c>
       <c r="C142" t="n">
-        <v>51067800</v>
+        <v>51067770</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -5128,7 +5116,7 @@
         <v>2016</v>
       </c>
       <c r="C143" t="n">
-        <v>51521500</v>
+        <v>51521507</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -5161,7 +5149,7 @@
         <v>2017</v>
       </c>
       <c r="C144" t="n">
-        <v>52506900</v>
+        <v>52506928</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -5194,7 +5182,7 @@
         <v>2018</v>
       </c>
       <c r="C145" t="n">
-        <v>54161000</v>
+        <v>54161014</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -5227,7 +5215,7 @@
         <v>2019</v>
       </c>
       <c r="C146" t="n">
-        <v>55354900</v>
+        <v>55354944</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -5260,7 +5248,7 @@
         <v>2020</v>
       </c>
       <c r="C147" t="n">
-        <v>55647700</v>
+        <v>55647705</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -5293,7 +5281,7 @@
         <v>2021</v>
       </c>
       <c r="C148" t="n">
-        <v>56805300</v>
+        <v>56805348</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -5326,7 +5314,7 @@
         <v>2022</v>
       </c>
       <c r="C149" t="n">
-        <v>59020000</v>
+        <v>59019998</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -5359,7 +5347,7 @@
         <v>2023</v>
       </c>
       <c r="C150" t="n">
-        <v>61190500</v>
+        <v>61190508</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -5392,7 +5380,7 @@
         <v>2024</v>
       </c>
       <c r="C151" t="n">
-        <v>62408700</v>
+        <v>62408729</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -5425,7 +5413,7 @@
         <v>2010</v>
       </c>
       <c r="C152" t="n">
-        <v>1652810</v>
+        <v>1652809</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -5458,7 +5446,7 @@
         <v>2011</v>
       </c>
       <c r="C153" t="n">
-        <v>1806080</v>
+        <v>1806075</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -5524,7 +5512,7 @@
         <v>2013</v>
       </c>
       <c r="C155" t="n">
-        <v>1927420</v>
+        <v>1927423</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -5557,7 +5545,7 @@
         <v>2014</v>
       </c>
       <c r="C156" t="n">
-        <v>1897550</v>
+        <v>1897551</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -5590,7 +5578,7 @@
         <v>2015</v>
       </c>
       <c r="C157" t="n">
-        <v>1903550</v>
+        <v>1903545</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -5623,7 +5611,7 @@
         <v>2016</v>
       </c>
       <c r="C158" t="n">
-        <v>1897920</v>
+        <v>1897921</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -5656,7 +5644,7 @@
         <v>2017</v>
       </c>
       <c r="C159" t="n">
-        <v>1904430</v>
+        <v>1904425</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -5689,7 +5677,7 @@
         <v>2018</v>
       </c>
       <c r="C160" t="n">
-        <v>1924030</v>
+        <v>1924034</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -5722,7 +5710,7 @@
         <v>2019</v>
       </c>
       <c r="C161" t="n">
-        <v>1951050</v>
+        <v>1951051</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -5755,7 +5743,7 @@
         <v>2020</v>
       </c>
       <c r="C162" t="n">
-        <v>1925790</v>
+        <v>1925789</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -5788,7 +5776,7 @@
         <v>2021</v>
       </c>
       <c r="C163" t="n">
-        <v>1980840</v>
+        <v>1980838</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -5821,7 +5809,7 @@
         <v>2022</v>
       </c>
       <c r="C164" t="n">
-        <v>2055790</v>
+        <v>2055794</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -5887,7 +5875,7 @@
         <v>2024</v>
       </c>
       <c r="C166" t="n">
-        <v>2056220</v>
+        <v>2056218</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -6877,7 +6865,7 @@
         <v>2010</v>
       </c>
       <c r="C196" t="n">
-        <v>12292700</v>
+        <v>12292716</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -6910,7 +6898,7 @@
         <v>2011</v>
       </c>
       <c r="C197" t="n">
-        <v>12128000</v>
+        <v>12127985</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -6943,7 +6931,7 @@
         <v>2012</v>
       </c>
       <c r="C198" t="n">
-        <v>13360300</v>
+        <v>13360280</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -6976,7 +6964,7 @@
         <v>2013</v>
       </c>
       <c r="C199" t="n">
-        <v>12518600</v>
+        <v>12518645</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -7009,7 +6997,7 @@
         <v>2014</v>
       </c>
       <c r="C200" t="n">
-        <v>12144600</v>
+        <v>12144598</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -7042,7 +7030,7 @@
         <v>2015</v>
       </c>
       <c r="C201" t="n">
-        <v>12566600</v>
+        <v>12566649</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -7075,7 +7063,7 @@
         <v>2016</v>
       </c>
       <c r="C202" t="n">
-        <v>12538900</v>
+        <v>12538927</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -7108,7 +7096,7 @@
         <v>2017</v>
       </c>
       <c r="C203" t="n">
-        <v>12937100</v>
+        <v>12937106</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -7141,7 +7129,7 @@
         <v>2018</v>
       </c>
       <c r="C204" t="n">
-        <v>12170800</v>
+        <v>12170757</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -7174,7 +7162,7 @@
         <v>2019</v>
       </c>
       <c r="C205" t="n">
-        <v>11882100</v>
+        <v>11882081</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -7207,7 +7195,7 @@
         <v>2020</v>
       </c>
       <c r="C206" t="n">
-        <v>11413000</v>
+        <v>11412995</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -7240,7 +7228,7 @@
         <v>2021</v>
       </c>
       <c r="C207" t="n">
-        <v>11494000</v>
+        <v>11494008</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -7273,7 +7261,7 @@
         <v>2022</v>
       </c>
       <c r="C208" t="n">
-        <v>11352400</v>
+        <v>11352410</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -7306,7 +7294,7 @@
         <v>2023</v>
       </c>
       <c r="C209" t="n">
-        <v>11348300</v>
+        <v>11348340</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -7339,7 +7327,7 @@
         <v>2024</v>
       </c>
       <c r="C210" t="n">
-        <v>11414100</v>
+        <v>11414080</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -7372,7 +7360,7 @@
         <v>2010</v>
       </c>
       <c r="C211" t="n">
-        <v>12011800</v>
+        <v>12011823</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -7405,7 +7393,7 @@
         <v>2011</v>
       </c>
       <c r="C212" t="n">
-        <v>11689900</v>
+        <v>11689937</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -7438,7 +7426,7 @@
         <v>2012</v>
       </c>
       <c r="C213" t="n">
-        <v>11579400</v>
+        <v>11579425</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -7471,7 +7459,7 @@
         <v>2013</v>
       </c>
       <c r="C214" t="n">
-        <v>11590300</v>
+        <v>11590326</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -7504,7 +7492,7 @@
         <v>2014</v>
       </c>
       <c r="C215" t="n">
-        <v>11726500</v>
+        <v>11726491</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -7537,7 +7525,7 @@
         <v>2015</v>
       </c>
       <c r="C216" t="n">
-        <v>9900580</v>
+        <v>9900582</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -7570,7 +7558,7 @@
         <v>2016</v>
       </c>
       <c r="C217" t="n">
-        <v>9952000</v>
+        <v>9952001</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -7603,7 +7591,7 @@
         <v>2017</v>
       </c>
       <c r="C218" t="n">
-        <v>9945040</v>
+        <v>9945037</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -7636,7 +7624,7 @@
         <v>2018</v>
       </c>
       <c r="C219" t="n">
-        <v>10041900</v>
+        <v>10041939</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -7669,7 +7657,7 @@
         <v>2019</v>
       </c>
       <c r="C220" t="n">
-        <v>10272700</v>
+        <v>10272694</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -7702,7 +7690,7 @@
         <v>2020</v>
       </c>
       <c r="C221" t="n">
-        <v>10332700</v>
+        <v>10332660</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -7735,7 +7723,7 @@
         <v>2021</v>
       </c>
       <c r="C222" t="n">
-        <v>10206600</v>
+        <v>10206570</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -7801,7 +7789,7 @@
         <v>2023</v>
       </c>
       <c r="C224" t="n">
-        <v>10176100</v>
+        <v>10176058</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -7834,7 +7822,7 @@
         <v>2024</v>
       </c>
       <c r="C225" t="n">
-        <v>10119400</v>
+        <v>10119363</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -7900,7 +7888,7 @@
         <v>2011</v>
       </c>
       <c r="C227" t="n">
-        <v>19829300</v>
+        <v>19829309</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -8032,7 +8020,7 @@
         <v>2015</v>
       </c>
       <c r="C231" t="n">
-        <v>20809100</v>
+        <v>20809054</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -8362,7 +8350,7 @@
         <v>2010</v>
       </c>
       <c r="C241" t="n">
-        <v>4928350</v>
+        <v>4928352</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -8428,7 +8416,7 @@
         <v>2012</v>
       </c>
       <c r="C243" t="n">
-        <v>4971350</v>
+        <v>4971351</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -8461,7 +8449,7 @@
         <v>2013</v>
       </c>
       <c r="C244" t="n">
-        <v>4721020</v>
+        <v>4721015</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -8494,7 +8482,7 @@
         <v>2014</v>
       </c>
       <c r="C245" t="n">
-        <v>4461350</v>
+        <v>4461352</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -8560,7 +8548,7 @@
         <v>2016</v>
       </c>
       <c r="C247" t="n">
-        <v>4414350</v>
+        <v>4414347</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -8626,7 +8614,7 @@
         <v>2018</v>
       </c>
       <c r="C249" t="n">
-        <v>4388480</v>
+        <v>4388476</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -8659,7 +8647,7 @@
         <v>2019</v>
       </c>
       <c r="C250" t="n">
-        <v>4404650</v>
+        <v>4404652</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -8692,7 +8680,7 @@
         <v>2020</v>
       </c>
       <c r="C251" t="n">
-        <v>4375700</v>
+        <v>4375699</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -8725,7 +8713,7 @@
         <v>2021</v>
       </c>
       <c r="C252" t="n">
-        <v>4402210</v>
+        <v>4402213</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -8758,7 +8746,7 @@
         <v>2022</v>
       </c>
       <c r="C253" t="n">
-        <v>4480470</v>
+        <v>4480469</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -8791,7 +8779,7 @@
         <v>2023</v>
       </c>
       <c r="C254" t="n">
-        <v>4562730</v>
+        <v>4562734</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -8824,7 +8812,7 @@
         <v>2024</v>
       </c>
       <c r="C255" t="n">
-        <v>4717530</v>
+        <v>4717531</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -8857,7 +8845,7 @@
         <v>2010</v>
       </c>
       <c r="C256" t="n">
-        <v>93666100</v>
+        <v>93666088</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -8890,7 +8878,7 @@
         <v>2011</v>
       </c>
       <c r="C257" t="n">
-        <v>96040900</v>
+        <v>96040913</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -8923,7 +8911,7 @@
         <v>2012</v>
       </c>
       <c r="C258" t="n">
-        <v>97188600</v>
+        <v>97188624</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -8956,7 +8944,7 @@
         <v>2013</v>
       </c>
       <c r="C259" t="n">
-        <v>96863100</v>
+        <v>96863107</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -8989,7 +8977,7 @@
         <v>2014</v>
       </c>
       <c r="C260" t="n">
-        <v>89914600</v>
+        <v>89914609</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -9022,7 +9010,7 @@
         <v>2015</v>
       </c>
       <c r="C261" t="n">
-        <v>87691200</v>
+        <v>87691238</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -9055,7 +9043,7 @@
         <v>2016</v>
       </c>
       <c r="C262" t="n">
-        <v>85955900</v>
+        <v>85955905</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -9088,7 +9076,7 @@
         <v>2017</v>
       </c>
       <c r="C263" t="n">
-        <v>83871500</v>
+        <v>83871543</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -9121,7 +9109,7 @@
         <v>2018</v>
       </c>
       <c r="C264" t="n">
-        <v>83342500</v>
+        <v>83342486</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -9154,7 +9142,7 @@
         <v>2019</v>
       </c>
       <c r="C265" t="n">
-        <v>79480800</v>
+        <v>79480756</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -9187,7 +9175,7 @@
         <v>2020</v>
       </c>
       <c r="C266" t="n">
-        <v>77581000</v>
+        <v>77581048</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -9220,7 +9208,7 @@
         <v>2021</v>
       </c>
       <c r="C267" t="n">
-        <v>78114900</v>
+        <v>78114933</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -9253,7 +9241,7 @@
         <v>2022</v>
       </c>
       <c r="C268" t="n">
-        <v>78502900</v>
+        <v>78502853</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -9286,7 +9274,7 @@
         <v>2023</v>
       </c>
       <c r="C269" t="n">
-        <v>78462900</v>
+        <v>78462925</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -9319,7 +9307,7 @@
         <v>2024</v>
       </c>
       <c r="C270" t="n">
-        <v>78673900</v>
+        <v>78673890</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -9352,7 +9340,7 @@
         <v>2010</v>
       </c>
       <c r="C271" t="n">
-        <v>4701470</v>
+        <v>4701474</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -9385,7 +9373,7 @@
         <v>2011</v>
       </c>
       <c r="C272" t="n">
-        <v>4906350</v>
+        <v>4906352</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -9418,7 +9406,7 @@
         <v>2012</v>
       </c>
       <c r="C273" t="n">
-        <v>5013680</v>
+        <v>5013676</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -9451,7 +9439,7 @@
         <v>2013</v>
       </c>
       <c r="C274" t="n">
-        <v>4880790</v>
+        <v>4880792</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -9517,7 +9505,7 @@
         <v>2015</v>
       </c>
       <c r="C276" t="n">
-        <v>4902010</v>
+        <v>4902009</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -9550,7 +9538,7 @@
         <v>2016</v>
       </c>
       <c r="C277" t="n">
-        <v>4875120</v>
+        <v>4875116</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -9583,7 +9571,7 @@
         <v>2017</v>
       </c>
       <c r="C278" t="n">
-        <v>4898870</v>
+        <v>4898872</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -9616,7 +9604,7 @@
         <v>2018</v>
       </c>
       <c r="C279" t="n">
-        <v>4971490</v>
+        <v>4971493</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -9649,7 +9637,7 @@
         <v>2019</v>
       </c>
       <c r="C280" t="n">
-        <v>5160310</v>
+        <v>5160309</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -9682,7 +9670,7 @@
         <v>2020</v>
       </c>
       <c r="C281" t="n">
-        <v>5234010</v>
+        <v>5234009</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -9715,7 +9703,7 @@
         <v>2021</v>
       </c>
       <c r="C282" t="n">
-        <v>5373870</v>
+        <v>5373865</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -9814,7 +9802,7 @@
         <v>2024</v>
       </c>
       <c r="C285" t="n">
-        <v>5919190</v>
+        <v>5919189</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -9847,7 +9835,7 @@
         <v>2010</v>
       </c>
       <c r="C286" t="n">
-        <v>4890980</v>
+        <v>4890979</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -9913,7 +9901,7 @@
         <v>2012</v>
       </c>
       <c r="C288" t="n">
-        <v>4997270</v>
+        <v>4997265</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -9946,7 +9934,7 @@
         <v>2013</v>
       </c>
       <c r="C289" t="n">
-        <v>4565980</v>
+        <v>4565976</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -9979,7 +9967,7 @@
         <v>2014</v>
       </c>
       <c r="C290" t="n">
-        <v>4267590</v>
+        <v>4267592</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -10012,7 +10000,7 @@
         <v>2015</v>
       </c>
       <c r="C291" t="n">
-        <v>4184050</v>
+        <v>4184053</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -10045,7 +10033,7 @@
         <v>2016</v>
       </c>
       <c r="C292" t="n">
-        <v>4204690</v>
+        <v>4204692</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -10078,7 +10066,7 @@
         <v>2017</v>
       </c>
       <c r="C293" t="n">
-        <v>4361330</v>
+        <v>4361329</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -10144,7 +10132,7 @@
         <v>2019</v>
       </c>
       <c r="C295" t="n">
-        <v>3704260</v>
+        <v>3704258</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -10177,7 +10165,7 @@
         <v>2020</v>
       </c>
       <c r="C296" t="n">
-        <v>3672000</v>
+        <v>3671995</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -10210,7 +10198,7 @@
         <v>2021</v>
       </c>
       <c r="C297" t="n">
-        <v>3726650</v>
+        <v>3726653</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -10243,7 +10231,7 @@
         <v>2022</v>
       </c>
       <c r="C298" t="n">
-        <v>3826340</v>
+        <v>3826338</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -10870,7 +10858,7 @@
         <v>2012</v>
       </c>
       <c r="C317" t="n">
-        <v>2630870</v>
+        <v>2630873</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -11002,7 +10990,7 @@
         <v>2016</v>
       </c>
       <c r="C321" t="n">
-        <v>2650270</v>
+        <v>2650273</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -11035,7 +11023,7 @@
         <v>2017</v>
       </c>
       <c r="C322" t="n">
-        <v>2464120</v>
+        <v>2464122</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -11101,7 +11089,7 @@
         <v>2019</v>
       </c>
       <c r="C324" t="n">
-        <v>2071650</v>
+        <v>2071652</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -11134,7 +11122,7 @@
         <v>2020</v>
       </c>
       <c r="C325" t="n">
-        <v>2051360</v>
+        <v>2051359</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -11167,7 +11155,7 @@
         <v>2021</v>
       </c>
       <c r="C326" t="n">
-        <v>2161730</v>
+        <v>2161725</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -11200,7 +11188,7 @@
         <v>2022</v>
       </c>
       <c r="C327" t="n">
-        <v>2167030</v>
+        <v>2167034</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -11266,7 +11254,7 @@
         <v>2024</v>
       </c>
       <c r="C329" t="n">
-        <v>2269870</v>
+        <v>2269872</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -11794,7 +11782,7 @@
         <v>2010</v>
       </c>
       <c r="C345" t="n">
-        <v>46952100</v>
+        <v>46952111</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -11827,7 +11815,7 @@
         <v>2011</v>
       </c>
       <c r="C346" t="n">
-        <v>50160200</v>
+        <v>50160222</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -11860,7 +11848,7 @@
         <v>2012</v>
       </c>
       <c r="C347" t="n">
-        <v>54086200</v>
+        <v>54086209</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -11893,7 +11881,7 @@
         <v>2013</v>
       </c>
       <c r="C348" t="n">
-        <v>56972800</v>
+        <v>56972803</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -11926,7 +11914,7 @@
         <v>2014</v>
       </c>
       <c r="C349" t="n">
-        <v>56905300</v>
+        <v>56905306</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -11959,7 +11947,7 @@
         <v>2015</v>
       </c>
       <c r="C350" t="n">
-        <v>54537200</v>
+        <v>54537230</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -11992,7 +11980,7 @@
         <v>2016</v>
       </c>
       <c r="C351" t="n">
-        <v>53001800</v>
+        <v>53001776</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -12025,7 +12013,7 @@
         <v>2017</v>
       </c>
       <c r="C352" t="n">
-        <v>50458900</v>
+        <v>50458854</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -12058,7 +12046,7 @@
         <v>2018</v>
       </c>
       <c r="C353" t="n">
-        <v>48285500</v>
+        <v>48285544</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -12091,7 +12079,7 @@
         <v>2019</v>
       </c>
       <c r="C354" t="n">
-        <v>48392900</v>
+        <v>48392944</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -12124,7 +12112,7 @@
         <v>2020</v>
       </c>
       <c r="C355" t="n">
-        <v>49350700</v>
+        <v>49350724</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -12157,7 +12145,7 @@
         <v>2021</v>
       </c>
       <c r="C356" t="n">
-        <v>50588700</v>
+        <v>50588734</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -12190,7 +12178,7 @@
         <v>2022</v>
       </c>
       <c r="C357" t="n">
-        <v>52589300</v>
+        <v>52589287</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -12223,7 +12211,7 @@
         <v>2023</v>
       </c>
       <c r="C358" t="n">
-        <v>52386600</v>
+        <v>52386550</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -12256,7 +12244,7 @@
         <v>2024</v>
       </c>
       <c r="C359" t="n">
-        <v>53190300</v>
+        <v>53190324</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -12289,7 +12277,7 @@
         <v>2010</v>
       </c>
       <c r="C360" t="n">
-        <v>12210400</v>
+        <v>12210377</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -12322,7 +12310,7 @@
         <v>2011</v>
       </c>
       <c r="C361" t="n">
-        <v>12334600</v>
+        <v>12334595</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -12355,7 +12343,7 @@
         <v>2012</v>
       </c>
       <c r="C362" t="n">
-        <v>11917600</v>
+        <v>11917565</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -12388,7 +12376,7 @@
         <v>2013</v>
       </c>
       <c r="C363" t="n">
-        <v>11991000</v>
+        <v>11990993</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -12421,7 +12409,7 @@
         <v>2014</v>
       </c>
       <c r="C364" t="n">
-        <v>11895600</v>
+        <v>11895627</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -12454,7 +12442,7 @@
         <v>2015</v>
       </c>
       <c r="C365" t="n">
-        <v>11714700</v>
+        <v>11714693</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -12487,7 +12475,7 @@
         <v>2016</v>
       </c>
       <c r="C366" t="n">
-        <v>11572100</v>
+        <v>11572085</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -12520,7 +12508,7 @@
         <v>2017</v>
       </c>
       <c r="C367" t="n">
-        <v>11764100</v>
+        <v>11764106</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -12553,7 +12541,7 @@
         <v>2018</v>
       </c>
       <c r="C368" t="n">
-        <v>11859500</v>
+        <v>11859548</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -12586,7 +12574,7 @@
         <v>2019</v>
       </c>
       <c r="C369" t="n">
-        <v>11909800</v>
+        <v>11909751</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -12619,7 +12607,7 @@
         <v>2020</v>
       </c>
       <c r="C370" t="n">
-        <v>11851100</v>
+        <v>11851054</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -12652,7 +12640,7 @@
         <v>2021</v>
       </c>
       <c r="C371" t="n">
-        <v>12445100</v>
+        <v>12445113</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -12685,7 +12673,7 @@
         <v>2022</v>
       </c>
       <c r="C372" t="n">
-        <v>12792300</v>
+        <v>12792302</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -12718,7 +12706,7 @@
         <v>2023</v>
       </c>
       <c r="C373" t="n">
-        <v>12830000</v>
+        <v>12829965</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -12751,7 +12739,7 @@
         <v>2024</v>
       </c>
       <c r="C374" t="n">
-        <v>12940900</v>
+        <v>12940913</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -13279,7 +13267,7 @@
         <v>2010</v>
       </c>
       <c r="C390" t="n">
-        <v>10992400</v>
+        <v>10992407</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -13312,7 +13300,7 @@
         <v>2011</v>
       </c>
       <c r="C391" t="n">
-        <v>11454300</v>
+        <v>11454252</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -13345,7 +13333,7 @@
         <v>2012</v>
       </c>
       <c r="C392" t="n">
-        <v>11848400</v>
+        <v>11848449</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -13378,7 +13366,7 @@
         <v>2013</v>
       </c>
       <c r="C393" t="n">
-        <v>12014400</v>
+        <v>12014368</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -13411,7 +13399,7 @@
         <v>2014</v>
       </c>
       <c r="C394" t="n">
-        <v>12312500</v>
+        <v>12312533</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -13444,7 +13432,7 @@
         <v>2015</v>
       </c>
       <c r="C395" t="n">
-        <v>12638800</v>
+        <v>12638827</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -13477,7 +13465,7 @@
         <v>2016</v>
       </c>
       <c r="C396" t="n">
-        <v>12543200</v>
+        <v>12543188</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -13510,7 +13498,7 @@
         <v>2017</v>
       </c>
       <c r="C397" t="n">
-        <v>12519300</v>
+        <v>12519313</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -13543,7 +13531,7 @@
         <v>2018</v>
       </c>
       <c r="C398" t="n">
-        <v>12626300</v>
+        <v>12626282</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -13576,7 +13564,7 @@
         <v>2019</v>
       </c>
       <c r="C399" t="n">
-        <v>12895900</v>
+        <v>12895854</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -13609,7 +13597,7 @@
         <v>2020</v>
       </c>
       <c r="C400" t="n">
-        <v>12791800</v>
+        <v>12791840</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -13642,7 +13630,7 @@
         <v>2021</v>
       </c>
       <c r="C401" t="n">
-        <v>13016200</v>
+        <v>13016153</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -13675,7 +13663,7 @@
         <v>2022</v>
       </c>
       <c r="C402" t="n">
-        <v>14764200</v>
+        <v>14764249</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -13708,7 +13696,7 @@
         <v>2023</v>
       </c>
       <c r="C403" t="n">
-        <v>14800100</v>
+        <v>14800126</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -13741,7 +13729,7 @@
         <v>2024</v>
       </c>
       <c r="C404" t="n">
-        <v>14922600</v>
+        <v>14922634</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -13807,7 +13795,7 @@
         <v>2011</v>
       </c>
       <c r="C406" t="n">
-        <v>2168550</v>
+        <v>2168548</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -13873,7 +13861,7 @@
         <v>2013</v>
       </c>
       <c r="C408" t="n">
-        <v>2283570</v>
+        <v>2283573</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -13906,7 +13894,7 @@
         <v>2014</v>
       </c>
       <c r="C409" t="n">
-        <v>2326390</v>
+        <v>2326386</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -13939,7 +13927,7 @@
         <v>2015</v>
       </c>
       <c r="C410" t="n">
-        <v>2353930</v>
+        <v>2353926</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -13972,7 +13960,7 @@
         <v>2016</v>
       </c>
       <c r="C411" t="n">
-        <v>2385760</v>
+        <v>2385757</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -14005,7 +13993,7 @@
         <v>2017</v>
       </c>
       <c r="C412" t="n">
-        <v>2443170</v>
+        <v>2443172</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -14038,7 +14026,7 @@
         <v>2018</v>
       </c>
       <c r="C413" t="n">
-        <v>2465860</v>
+        <v>2465857</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -14071,7 +14059,7 @@
         <v>2019</v>
       </c>
       <c r="C414" t="n">
-        <v>2511980</v>
+        <v>2511979</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -14104,7 +14092,7 @@
         <v>2020</v>
       </c>
       <c r="C415" t="n">
-        <v>2550900</v>
+        <v>2550895</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -14137,7 +14125,7 @@
         <v>2021</v>
       </c>
       <c r="C416" t="n">
-        <v>2607270</v>
+        <v>2607268</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -14236,7 +14224,7 @@
         <v>2024</v>
       </c>
       <c r="C419" t="n">
-        <v>2772550</v>
+        <v>2772546</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -14434,7 +14422,7 @@
         <v>2015</v>
       </c>
       <c r="C425" t="n">
-        <v>12454600</v>
+        <v>12454575.01</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -14467,7 +14455,7 @@
         <v>2016</v>
       </c>
       <c r="C426" t="n">
-        <v>12485000</v>
+        <v>12485045</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -14500,7 +14488,7 @@
         <v>2017</v>
       </c>
       <c r="C427" t="n">
-        <v>12636400</v>
+        <v>12636359</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -14533,7 +14521,7 @@
         <v>2018</v>
       </c>
       <c r="C428" t="n">
-        <v>12704300</v>
+        <v>12704262</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -14566,7 +14554,7 @@
         <v>2019</v>
       </c>
       <c r="C429" t="n">
-        <v>13101400</v>
+        <v>13101360</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -14599,7 +14587,7 @@
         <v>2020</v>
       </c>
       <c r="C430" t="n">
-        <v>12999800</v>
+        <v>12999812</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -14632,7 +14620,7 @@
         <v>2021</v>
       </c>
       <c r="C431" t="n">
-        <v>13286900</v>
+        <v>13286894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -14665,7 +14653,7 @@
         <v>2022</v>
       </c>
       <c r="C432" t="n">
-        <v>13673000</v>
+        <v>13672951</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -14698,7 +14686,7 @@
         <v>2023</v>
       </c>
       <c r="C433" t="n">
-        <v>13620800</v>
+        <v>13620756</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -14731,7 +14719,7 @@
         <v>2024</v>
       </c>
       <c r="C434" t="n">
-        <v>13591600</v>
+        <v>13591615</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -14764,7 +14752,7 @@
         <v>2010</v>
       </c>
       <c r="C435" t="n">
-        <v>53928800</v>
+        <v>53928830</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -14797,7 +14785,7 @@
         <v>2011</v>
       </c>
       <c r="C436" t="n">
-        <v>55576500</v>
+        <v>55576481</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -14830,7 +14818,7 @@
         <v>2012</v>
       </c>
       <c r="C437" t="n">
-        <v>59343700</v>
+        <v>59343693</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -14896,7 +14884,7 @@
         <v>2014</v>
       </c>
       <c r="C439" t="n">
-        <v>61170200</v>
+        <v>61170229</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -14929,7 +14917,7 @@
         <v>2015</v>
       </c>
       <c r="C440" t="n">
-        <v>60720100</v>
+        <v>60720073</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -14962,7 +14950,7 @@
         <v>2016</v>
       </c>
       <c r="C441" t="n">
-        <v>56717900</v>
+        <v>56717856</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -14995,7 +14983,7 @@
         <v>2017</v>
       </c>
       <c r="C442" t="n">
-        <v>55714700</v>
+        <v>55714733</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -15028,7 +15016,7 @@
         <v>2018</v>
       </c>
       <c r="C443" t="n">
-        <v>53933600</v>
+        <v>53933592</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -15061,7 +15049,7 @@
         <v>2019</v>
       </c>
       <c r="C444" t="n">
-        <v>54842900</v>
+        <v>54842940</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -15094,7 +15082,7 @@
         <v>2020</v>
       </c>
       <c r="C445" t="n">
-        <v>53977700</v>
+        <v>53977690</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -15127,7 +15115,7 @@
         <v>2021</v>
       </c>
       <c r="C446" t="n">
-        <v>55925900</v>
+        <v>55925908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -15160,7 +15148,7 @@
         <v>2022</v>
       </c>
       <c r="C447" t="n">
-        <v>49304300</v>
+        <v>49304301</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -15193,7 +15181,7 @@
         <v>2023</v>
       </c>
       <c r="C448" t="n">
-        <v>50328100</v>
+        <v>50328105</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -15226,7 +15214,7 @@
         <v>2010</v>
       </c>
       <c r="C449" t="n">
-        <v>2550590</v>
+        <v>2550592</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -15259,7 +15247,7 @@
         <v>2011</v>
       </c>
       <c r="C450" t="n">
-        <v>3217260</v>
+        <v>3217261</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -15292,7 +15280,7 @@
         <v>2012</v>
       </c>
       <c r="C451" t="n">
-        <v>3584280</v>
+        <v>3584283</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -15325,7 +15313,7 @@
         <v>2013</v>
       </c>
       <c r="C452" t="n">
-        <v>3696830</v>
+        <v>3696834</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -15358,7 +15346,7 @@
         <v>2014</v>
       </c>
       <c r="C453" t="n">
-        <v>3738130</v>
+        <v>3738125</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -15391,7 +15379,7 @@
         <v>2015</v>
       </c>
       <c r="C454" t="n">
-        <v>3713140</v>
+        <v>3713137</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -15457,7 +15445,7 @@
         <v>2017</v>
       </c>
       <c r="C456" t="n">
-        <v>3746640</v>
+        <v>3746644</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -15490,7 +15478,7 @@
         <v>2018</v>
       </c>
       <c r="C457" t="n">
-        <v>3636930</v>
+        <v>3636931</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -15523,7 +15511,7 @@
         <v>2019</v>
       </c>
       <c r="C458" t="n">
-        <v>3613850</v>
+        <v>3613846</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -15556,7 +15544,7 @@
         <v>2020</v>
       </c>
       <c r="C459" t="n">
-        <v>3420380</v>
+        <v>3420383</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -15589,7 +15577,7 @@
         <v>2021</v>
       </c>
       <c r="C460" t="n">
-        <v>3900180</v>
+        <v>3900179</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -15622,7 +15610,7 @@
         <v>2022</v>
       </c>
       <c r="C461" t="n">
-        <v>4170330</v>
+        <v>4170329</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -15655,7 +15643,7 @@
         <v>2023</v>
       </c>
       <c r="C462" t="n">
-        <v>3973270</v>
+        <v>3973269</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -15688,7 +15676,7 @@
         <v>2024</v>
       </c>
       <c r="C463" t="n">
-        <v>3644490</v>
+        <v>3644487</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -15721,7 +15709,7 @@
         <v>2010</v>
       </c>
       <c r="C464" t="n">
-        <v>3978240</v>
+        <v>3978242</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -15754,7 +15742,7 @@
         <v>2011</v>
       </c>
       <c r="C465" t="n">
-        <v>4430340</v>
+        <v>4430344</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -15787,7 +15775,7 @@
         <v>2012</v>
       </c>
       <c r="C466" t="n">
-        <v>4698580</v>
+        <v>4698582</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -15820,7 +15808,7 @@
         <v>2013</v>
       </c>
       <c r="C467" t="n">
-        <v>4993120</v>
+        <v>4993119</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -15853,7 +15841,7 @@
         <v>2014</v>
       </c>
       <c r="C468" t="n">
-        <v>5400770</v>
+        <v>5400766</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -15919,7 +15907,7 @@
         <v>2016</v>
       </c>
       <c r="C470" t="n">
-        <v>5531880</v>
+        <v>5531875</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -15952,7 +15940,7 @@
         <v>2017</v>
       </c>
       <c r="C471" t="n">
-        <v>5502400</v>
+        <v>5502395</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -15985,7 +15973,7 @@
         <v>2018</v>
       </c>
       <c r="C472" t="n">
-        <v>5459240</v>
+        <v>5459239</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -16018,7 +16006,7 @@
         <v>2019</v>
       </c>
       <c r="C473" t="n">
-        <v>5382060</v>
+        <v>5382059</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -16051,7 +16039,7 @@
         <v>2020</v>
       </c>
       <c r="C474" t="n">
-        <v>5100100</v>
+        <v>5100101</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -16084,7 +16072,7 @@
         <v>2021</v>
       </c>
       <c r="C475" t="n">
-        <v>5552600</v>
+        <v>5552599</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -16117,7 +16105,7 @@
         <v>2022</v>
       </c>
       <c r="C476" t="n">
-        <v>5844480</v>
+        <v>5844482</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -16183,7 +16171,7 @@
         <v>2024</v>
       </c>
       <c r="C478" t="n">
-        <v>6138030</v>
+        <v>6138032</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -16216,7 +16204,7 @@
         <v>2010</v>
       </c>
       <c r="C479" t="n">
-        <v>5925010</v>
+        <v>5925012</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -16249,7 +16237,7 @@
         <v>2011</v>
       </c>
       <c r="C480" t="n">
-        <v>5983060</v>
+        <v>5983059</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -16282,7 +16270,7 @@
         <v>2012</v>
       </c>
       <c r="C481" t="n">
-        <v>6094470</v>
+        <v>6094466</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -16315,7 +16303,7 @@
         <v>2013</v>
       </c>
       <c r="C482" t="n">
-        <v>6208410</v>
+        <v>6208412</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -16348,7 +16336,7 @@
         <v>2014</v>
       </c>
       <c r="C483" t="n">
-        <v>6378100</v>
+        <v>6378095</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -16381,7 +16369,7 @@
         <v>2015</v>
       </c>
       <c r="C484" t="n">
-        <v>6675550</v>
+        <v>6675553</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -16414,7 +16402,7 @@
         <v>2016</v>
       </c>
       <c r="C485" t="n">
-        <v>6989900</v>
+        <v>6989902</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -16447,7 +16435,7 @@
         <v>2017</v>
       </c>
       <c r="C486" t="n">
-        <v>7117750</v>
+        <v>7117753</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -16480,7 +16468,7 @@
         <v>2018</v>
       </c>
       <c r="C487" t="n">
-        <v>7241700</v>
+        <v>7241702</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -16513,7 +16501,7 @@
         <v>2019</v>
       </c>
       <c r="C488" t="n">
-        <v>7399530</v>
+        <v>7399534</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -16546,7 +16534,7 @@
         <v>2020</v>
       </c>
       <c r="C489" t="n">
-        <v>7289710</v>
+        <v>7289707</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -16579,7 +16567,7 @@
         <v>2021</v>
       </c>
       <c r="C490" t="n">
-        <v>7362330</v>
+        <v>7362325</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -16612,7 +16600,7 @@
         <v>2022</v>
       </c>
       <c r="C491" t="n">
-        <v>7445150</v>
+        <v>7445151</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -16678,7 +16666,7 @@
         <v>2024</v>
       </c>
       <c r="C493" t="n">
-        <v>7707680</v>
+        <v>7707684</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -16711,7 +16699,7 @@
         <v>2010</v>
       </c>
       <c r="C494" t="n">
-        <v>131.875</v>
+        <v>131.874825576119</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -16744,7 +16732,7 @@
         <v>2011</v>
       </c>
       <c r="C495" t="n">
-        <v>109.85</v>
+        <v>109.850061797213</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -16777,7 +16765,7 @@
         <v>2012</v>
       </c>
       <c r="C496" t="n">
-        <v>113.697</v>
+        <v>113.697353797808</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -16810,7 +16798,7 @@
         <v>2013</v>
       </c>
       <c r="C497" t="n">
-        <v>114.5</v>
+        <v>114.499722499571</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -16843,7 +16831,7 @@
         <v>2014</v>
       </c>
       <c r="C498" t="n">
-        <v>118.365</v>
+        <v>118.365417451689</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -16876,7 +16864,7 @@
         <v>2015</v>
       </c>
       <c r="C499" t="n">
-        <v>118.599</v>
+        <v>118.599112617962</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -16909,7 +16897,7 @@
         <v>2016</v>
       </c>
       <c r="C500" t="n">
-        <v>117.671</v>
+        <v>117.670797483754</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -16942,7 +16930,7 @@
         <v>2017</v>
       </c>
       <c r="C501" t="n">
-        <v>119.676</v>
+        <v>119.676441862212</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -16975,7 +16963,7 @@
         <v>2018</v>
       </c>
       <c r="C502" t="n">
-        <v>123</v>
+        <v>123.000001718234</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -17008,7 +16996,7 @@
         <v>2019</v>
       </c>
       <c r="C503" t="n">
-        <v>124.614</v>
+        <v>124.613701509519</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -17041,7 +17029,7 @@
         <v>2020</v>
       </c>
       <c r="C504" t="n">
-        <v>120.682</v>
+        <v>120.682370700808</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -17074,7 +17062,7 @@
         <v>2021</v>
       </c>
       <c r="C505" t="n">
-        <v>125.395</v>
+        <v>125.395134877327</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -17107,7 +17095,7 @@
         <v>2022</v>
       </c>
       <c r="C506" t="n">
-        <v>130.54</v>
+        <v>130.540072214196</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -17140,7 +17128,7 @@
         <v>2023</v>
       </c>
       <c r="C507" t="n">
-        <v>134.52</v>
+        <v>134.519957069953</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -17173,7 +17161,7 @@
         <v>2024</v>
       </c>
       <c r="C508" t="n">
-        <v>134.887</v>
+        <v>134.88694751567</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -17206,7 +17194,7 @@
         <v>2010</v>
       </c>
       <c r="C509" t="n">
-        <v>146.334</v>
+        <v>146.334314075685</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -17239,7 +17227,7 @@
         <v>2011</v>
       </c>
       <c r="C510" t="n">
-        <v>155.155</v>
+        <v>155.15499918387</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -17272,7 +17260,7 @@
         <v>2012</v>
       </c>
       <c r="C511" t="n">
-        <v>161.156</v>
+        <v>161.155633431895</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -17305,7 +17293,7 @@
         <v>2013</v>
       </c>
       <c r="C512" t="n">
-        <v>156.483</v>
+        <v>156.483488704585</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -17338,7 +17326,7 @@
         <v>2014</v>
       </c>
       <c r="C513" t="n">
-        <v>151.531</v>
+        <v>151.531145320495</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -17371,7 +17359,7 @@
         <v>2015</v>
       </c>
       <c r="C514" t="n">
-        <v>155.837</v>
+        <v>155.837138171172</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -17404,7 +17392,7 @@
         <v>2016</v>
       </c>
       <c r="C515" t="n">
-        <v>126.798</v>
+        <v>126.797525496643</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -17437,7 +17425,7 @@
         <v>2017</v>
       </c>
       <c r="C516" t="n">
-        <v>123.415</v>
+        <v>123.414865109678</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -17470,7 +17458,7 @@
         <v>2018</v>
       </c>
       <c r="C517" t="n">
-        <v>124.23</v>
+        <v>124.230205900482</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -17503,7 +17491,7 @@
         <v>2019</v>
       </c>
       <c r="C518" t="n">
-        <v>120.776</v>
+        <v>120.776373862218</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -17536,7 +17524,7 @@
         <v>2020</v>
       </c>
       <c r="C519" t="n">
-        <v>120.132</v>
+        <v>120.131806593244</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -17569,7 +17557,7 @@
         <v>2021</v>
       </c>
       <c r="C520" t="n">
-        <v>121.358</v>
+        <v>121.357731973824</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -17602,7 +17590,7 @@
         <v>2022</v>
       </c>
       <c r="C521" t="n">
-        <v>121.166</v>
+        <v>121.16645744796</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -17635,7 +17623,7 @@
         <v>2023</v>
       </c>
       <c r="C522" t="n">
-        <v>121.746</v>
+        <v>121.746207105931</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -17668,7 +17656,7 @@
         <v>2024</v>
       </c>
       <c r="C523" t="n">
-        <v>124.459</v>
+        <v>124.45929984531</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -17701,7 +17689,7 @@
         <v>2010</v>
       </c>
       <c r="C524" t="n">
-        <v>99.489</v>
+        <v>99.489026332669</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -17734,7 +17722,7 @@
         <v>2011</v>
       </c>
       <c r="C525" t="n">
-        <v>109.334</v>
+        <v>109.333848306261</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -17767,7 +17755,7 @@
         <v>2012</v>
       </c>
       <c r="C526" t="n">
-        <v>107.989</v>
+        <v>107.988529658291</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -17800,7 +17788,7 @@
         <v>2013</v>
       </c>
       <c r="C527" t="n">
-        <v>106.583</v>
+        <v>106.583186813615</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -17833,7 +17821,7 @@
         <v>2014</v>
       </c>
       <c r="C528" t="n">
-        <v>109.567</v>
+        <v>109.566699179266</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -17866,7 +17854,7 @@
         <v>2015</v>
       </c>
       <c r="C529" t="n">
-        <v>109.682</v>
+        <v>109.682113433509</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -17899,7 +17887,7 @@
         <v>2016</v>
       </c>
       <c r="C530" t="n">
-        <v>103.248</v>
+        <v>103.248460646417</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -17932,7 +17920,7 @@
         <v>2017</v>
       </c>
       <c r="C531" t="n">
-        <v>101.59</v>
+        <v>101.589906615934</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -17965,7 +17953,7 @@
         <v>2018</v>
       </c>
       <c r="C532" t="n">
-        <v>102.987</v>
+        <v>102.987275423455</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -17998,7 +17986,7 @@
         <v>2019</v>
       </c>
       <c r="C533" t="n">
-        <v>106.328</v>
+        <v>106.328337689377</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -18031,7 +18019,7 @@
         <v>2020</v>
       </c>
       <c r="C534" t="n">
-        <v>101.597</v>
+        <v>101.596683471276</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -18064,7 +18052,7 @@
         <v>2021</v>
       </c>
       <c r="C535" t="n">
-        <v>105.694</v>
+        <v>105.693559477177</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -18097,7 +18085,7 @@
         <v>2022</v>
       </c>
       <c r="C536" t="n">
-        <v>107.506</v>
+        <v>107.506296074404</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -18130,7 +18118,7 @@
         <v>2023</v>
       </c>
       <c r="C537" t="n">
-        <v>107.687</v>
+        <v>107.686732782159</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -18163,7 +18151,7 @@
         <v>2024</v>
       </c>
       <c r="C538" t="n">
-        <v>109.543</v>
+        <v>109.543149535867</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -18196,7 +18184,7 @@
         <v>2010</v>
       </c>
       <c r="C539" t="n">
-        <v>111.132</v>
+        <v>111.131540934105</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -18229,7 +18217,7 @@
         <v>2011</v>
       </c>
       <c r="C540" t="n">
-        <v>113.202</v>
+        <v>113.201845409997</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -18262,7 +18250,7 @@
         <v>2012</v>
       </c>
       <c r="C541" t="n">
-        <v>110.856</v>
+        <v>110.856223685615</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -18295,7 +18283,7 @@
         <v>2013</v>
       </c>
       <c r="C542" t="n">
-        <v>110.349</v>
+        <v>110.348677756715</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -18328,7 +18316,7 @@
         <v>2014</v>
       </c>
       <c r="C543" t="n">
-        <v>113.6</v>
+        <v>113.600257053471</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -18361,7 +18349,7 @@
         <v>2015</v>
       </c>
       <c r="C544" t="n">
-        <v>113.292</v>
+        <v>113.29233233425</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -18394,7 +18382,7 @@
         <v>2016</v>
       </c>
       <c r="C545" t="n">
-        <v>110.749</v>
+        <v>110.74871736226</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -18427,7 +18415,7 @@
         <v>2017</v>
       </c>
       <c r="C546" t="n">
-        <v>99.8304</v>
+        <v>99.8303971992992</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -18460,7 +18448,7 @@
         <v>2018</v>
       </c>
       <c r="C547" t="n">
-        <v>100.164</v>
+        <v>100.164027018171</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -18493,7 +18481,7 @@
         <v>2019</v>
       </c>
       <c r="C548" t="n">
-        <v>100.165</v>
+        <v>100.164960666171</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -18526,7 +18514,7 @@
         <v>2020</v>
       </c>
       <c r="C549" t="n">
-        <v>99.9101</v>
+        <v>99.91006149249741</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -18559,7 +18547,7 @@
         <v>2021</v>
       </c>
       <c r="C550" t="n">
-        <v>101.463</v>
+        <v>101.462935633736</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -18592,7 +18580,7 @@
         <v>2022</v>
       </c>
       <c r="C551" t="n">
-        <v>101.68</v>
+        <v>101.680355820653</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -18625,7 +18613,7 @@
         <v>2023</v>
       </c>
       <c r="C552" t="n">
-        <v>103.196</v>
+        <v>103.196426365374</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -18658,7 +18646,7 @@
         <v>2024</v>
       </c>
       <c r="C553" t="n">
-        <v>103.905</v>
+        <v>103.90465332676</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -18691,7 +18679,7 @@
         <v>2010</v>
       </c>
       <c r="C554" t="n">
-        <v>108.873</v>
+        <v>108.873353765855</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -18724,7 +18712,7 @@
         <v>2011</v>
       </c>
       <c r="C555" t="n">
-        <v>112.902</v>
+        <v>112.901923256589</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -18757,7 +18745,7 @@
         <v>2012</v>
       </c>
       <c r="C556" t="n">
-        <v>112.822</v>
+        <v>112.822416305227</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -18790,7 +18778,7 @@
         <v>2013</v>
       </c>
       <c r="C557" t="n">
-        <v>117.434</v>
+        <v>117.433516760028</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -18823,7 +18811,7 @@
         <v>2014</v>
       </c>
       <c r="C558" t="n">
-        <v>120.366</v>
+        <v>120.366076944418</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -18856,7 +18844,7 @@
         <v>2015</v>
       </c>
       <c r="C559" t="n">
-        <v>120.67</v>
+        <v>120.669626204229</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -18889,7 +18877,7 @@
         <v>2016</v>
       </c>
       <c r="C560" t="n">
-        <v>120.432</v>
+        <v>120.431507778029</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -18922,7 +18910,7 @@
         <v>2017</v>
       </c>
       <c r="C561" t="n">
-        <v>120.213</v>
+        <v>120.212652133209</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -18955,7 +18943,7 @@
         <v>2018</v>
       </c>
       <c r="C562" t="n">
-        <v>122.57</v>
+        <v>122.56975741957</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -18988,7 +18976,7 @@
         <v>2019</v>
       </c>
       <c r="C563" t="n">
-        <v>123.23</v>
+        <v>123.229810991965</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -19021,7 +19009,7 @@
         <v>2020</v>
       </c>
       <c r="C564" t="n">
-        <v>125.165</v>
+        <v>125.164732031333</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -19054,7 +19042,7 @@
         <v>2021</v>
       </c>
       <c r="C565" t="n">
-        <v>127.117</v>
+        <v>127.117317282369</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -19087,7 +19075,7 @@
         <v>2022</v>
       </c>
       <c r="C566" t="n">
-        <v>128.315</v>
+        <v>128.314999383533</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -19120,7 +19108,7 @@
         <v>2023</v>
       </c>
       <c r="C567" t="n">
-        <v>128.979</v>
+        <v>128.979176539764</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -19153,7 +19141,7 @@
         <v>2024</v>
       </c>
       <c r="C568" t="n">
-        <v>131.123</v>
+        <v>131.123016605614</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -19186,7 +19174,7 @@
         <v>2010</v>
       </c>
       <c r="C569" t="n">
-        <v>137.14</v>
+        <v>137.140251847404</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -19219,7 +19207,7 @@
         <v>2011</v>
       </c>
       <c r="C570" t="n">
-        <v>141.938</v>
+        <v>141.938313217096</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -19252,7 +19240,7 @@
         <v>2012</v>
       </c>
       <c r="C571" t="n">
-        <v>147.338</v>
+        <v>147.337862138845</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -19285,7 +19273,7 @@
         <v>2013</v>
       </c>
       <c r="C572" t="n">
-        <v>144.355</v>
+        <v>144.355146876635</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -19318,7 +19306,7 @@
         <v>2014</v>
       </c>
       <c r="C573" t="n">
-        <v>131.335</v>
+        <v>131.33514197996</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -19351,7 +19339,7 @@
         <v>2015</v>
       </c>
       <c r="C574" t="n">
-        <v>128.103</v>
+        <v>128.103256321093</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -19384,7 +19372,7 @@
         <v>2016</v>
       </c>
       <c r="C575" t="n">
-        <v>125.906</v>
+        <v>125.906027330453</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -19417,7 +19405,7 @@
         <v>2017</v>
       </c>
       <c r="C576" t="n">
-        <v>120.596</v>
+        <v>120.595632675282</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -19450,7 +19438,7 @@
         <v>2018</v>
       </c>
       <c r="C577" t="n">
-        <v>119.395</v>
+        <v>119.394511829255</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -19483,7 +19471,7 @@
         <v>2019</v>
       </c>
       <c r="C578" t="n">
-        <v>116.617</v>
+        <v>116.616975862125</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -19516,7 +19504,7 @@
         <v>2020</v>
       </c>
       <c r="C579" t="n">
-        <v>114.597</v>
+        <v>114.596737765322</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -19549,7 +19537,7 @@
         <v>2021</v>
       </c>
       <c r="C580" t="n">
-        <v>114.912</v>
+        <v>114.911988483727</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -19582,7 +19570,7 @@
         <v>2022</v>
       </c>
       <c r="C581" t="n">
-        <v>116.679</v>
+        <v>116.679163253179</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -19615,7 +19603,7 @@
         <v>2023</v>
       </c>
       <c r="C582" t="n">
-        <v>117.933</v>
+        <v>117.932685806225</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -19648,7 +19636,7 @@
         <v>2024</v>
       </c>
       <c r="C583" t="n">
-        <v>118.067</v>
+        <v>118.067152838789</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -19681,7 +19669,7 @@
         <v>2010</v>
       </c>
       <c r="C584" t="n">
-        <v>123.133</v>
+        <v>123.133007859014</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -19714,7 +19702,7 @@
         <v>2011</v>
       </c>
       <c r="C585" t="n">
-        <v>126.56</v>
+        <v>126.559628770302</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -19747,7 +19735,7 @@
         <v>2012</v>
       </c>
       <c r="C586" t="n">
-        <v>128.744</v>
+        <v>128.74435044617</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -19780,7 +19768,7 @@
         <v>2013</v>
       </c>
       <c r="C587" t="n">
-        <v>127.863</v>
+        <v>127.862906976744</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -19813,7 +19801,7 @@
         <v>2014</v>
       </c>
       <c r="C588" t="n">
-        <v>129.043</v>
+        <v>129.042983271375</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -19846,7 +19834,7 @@
         <v>2015</v>
       </c>
       <c r="C589" t="n">
-        <v>128.632</v>
+        <v>128.631974994212</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -19879,7 +19867,7 @@
         <v>2016</v>
       </c>
       <c r="C590" t="n">
-        <v>130.335</v>
+        <v>130.334521209334</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -19912,7 +19900,7 @@
         <v>2017</v>
       </c>
       <c r="C591" t="n">
-        <v>133.94</v>
+        <v>133.940473480537</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -19945,7 +19933,7 @@
         <v>2018</v>
       </c>
       <c r="C592" t="n">
-        <v>134.844</v>
+        <v>134.843630644799</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -19978,7 +19966,7 @@
         <v>2019</v>
       </c>
       <c r="C593" t="n">
-        <v>137.761</v>
+        <v>137.76052748227</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -20011,7 +19999,7 @@
         <v>2020</v>
       </c>
       <c r="C594" t="n">
-        <v>135.589</v>
+        <v>135.588846364133</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -20044,7 +20032,7 @@
         <v>2021</v>
       </c>
       <c r="C595" t="n">
-        <v>142.051</v>
+        <v>142.051408905141</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -20077,7 +20065,7 @@
         <v>2022</v>
       </c>
       <c r="C596" t="n">
-        <v>146.716</v>
+        <v>146.71583605521</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -20110,7 +20098,7 @@
         <v>2023</v>
       </c>
       <c r="C597" t="n">
-        <v>148.334</v>
+        <v>148.333712748344</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -20143,7 +20131,7 @@
         <v>2024</v>
       </c>
       <c r="C598" t="n">
-        <v>156.218</v>
+        <v>156.218025662252</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -20176,7 +20164,7 @@
         <v>2010</v>
       </c>
       <c r="C599" t="n">
-        <v>109.364</v>
+        <v>109.364084468464</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -20209,7 +20197,7 @@
         <v>2011</v>
       </c>
       <c r="C600" t="n">
-        <v>112.419</v>
+        <v>112.41947815744</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -20242,7 +20230,7 @@
         <v>2012</v>
       </c>
       <c r="C601" t="n">
-        <v>114.192</v>
+        <v>114.191945537857</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -20275,7 +20263,7 @@
         <v>2013</v>
       </c>
       <c r="C602" t="n">
-        <v>123.435</v>
+        <v>123.435398879553</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -20308,7 +20296,7 @@
         <v>2014</v>
       </c>
       <c r="C603" t="n">
-        <v>122.309</v>
+        <v>122.308668591557</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -20341,7 +20329,7 @@
         <v>2015</v>
       </c>
       <c r="C604" t="n">
-        <v>117.401</v>
+        <v>117.401165117624</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -20374,7 +20362,7 @@
         <v>2016</v>
       </c>
       <c r="C605" t="n">
-        <v>125.024</v>
+        <v>125.024012174369</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -20407,7 +20395,7 @@
         <v>2017</v>
       </c>
       <c r="C606" t="n">
-        <v>132.003</v>
+        <v>132.003261888443</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -20440,7 +20428,7 @@
         <v>2018</v>
       </c>
       <c r="C607" t="n">
-        <v>128.946</v>
+        <v>128.945577229674</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -20473,7 +20461,7 @@
         <v>2019</v>
       </c>
       <c r="C608" t="n">
-        <v>128.292</v>
+        <v>128.292298108313</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -20506,7 +20494,7 @@
         <v>2020</v>
       </c>
       <c r="C609" t="n">
-        <v>128.425</v>
+        <v>128.424798814302</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -20539,7 +20527,7 @@
         <v>2021</v>
       </c>
       <c r="C610" t="n">
-        <v>127.125</v>
+        <v>127.125099449404</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -20572,7 +20560,7 @@
         <v>2022</v>
       </c>
       <c r="C611" t="n">
-        <v>124.158</v>
+        <v>124.158264349285</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -20605,7 +20593,7 @@
         <v>2023</v>
       </c>
       <c r="C612" t="n">
-        <v>124.663</v>
+        <v>124.662572774586</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -20638,7 +20626,7 @@
         <v>2024</v>
       </c>
       <c r="C613" t="n">
-        <v>129.151</v>
+        <v>129.150921864378</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -20671,7 +20659,7 @@
         <v>2010</v>
       </c>
       <c r="C614" t="n">
-        <v>115.734</v>
+        <v>115.734472895239</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -20704,7 +20692,7 @@
         <v>2011</v>
       </c>
       <c r="C615" t="n">
-        <v>128.763</v>
+        <v>128.762868998962</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -20737,7 +20725,7 @@
         <v>2012</v>
       </c>
       <c r="C616" t="n">
-        <v>130.416</v>
+        <v>130.416027276514</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -20770,7 +20758,7 @@
         <v>2013</v>
       </c>
       <c r="C617" t="n">
-        <v>125.213</v>
+        <v>125.21344682497</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -20803,7 +20791,7 @@
         <v>2014</v>
       </c>
       <c r="C618" t="n">
-        <v>126.869</v>
+        <v>126.869141573913</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -20836,7 +20824,7 @@
         <v>2015</v>
       </c>
       <c r="C619" t="n">
-        <v>124.554</v>
+        <v>124.553508356615</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -20869,7 +20857,7 @@
         <v>2016</v>
       </c>
       <c r="C620" t="n">
-        <v>121.941</v>
+        <v>121.941164424922</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -20902,7 +20890,7 @@
         <v>2017</v>
       </c>
       <c r="C621" t="n">
-        <v>123.862</v>
+        <v>123.86211468599</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -20935,7 +20923,7 @@
         <v>2018</v>
       </c>
       <c r="C622" t="n">
-        <v>124.55</v>
+        <v>124.550124408336</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -20968,7 +20956,7 @@
         <v>2019</v>
       </c>
       <c r="C623" t="n">
-        <v>124.573</v>
+        <v>124.573359763273</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -21001,7 +20989,7 @@
         <v>2020</v>
       </c>
       <c r="C624" t="n">
-        <v>124.37</v>
+        <v>124.370019531752</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -21034,7 +21022,7 @@
         <v>2021</v>
       </c>
       <c r="C625" t="n">
-        <v>125.604</v>
+        <v>125.604137839658</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -21067,7 +21055,7 @@
         <v>2022</v>
       </c>
       <c r="C626" t="n">
-        <v>126.484</v>
+        <v>126.48354098254</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -21100,7 +21088,7 @@
         <v>2023</v>
       </c>
       <c r="C627" t="n">
-        <v>126.717</v>
+        <v>126.717092547985</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -21133,7 +21121,7 @@
         <v>2024</v>
       </c>
       <c r="C628" t="n">
-        <v>126.687</v>
+        <v>126.686532566268</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -21166,7 +21154,7 @@
         <v>2010</v>
       </c>
       <c r="C629" t="n">
-        <v>109.712</v>
+        <v>109.711571858447</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -21199,7 +21187,7 @@
         <v>2011</v>
       </c>
       <c r="C630" t="n">
-        <v>111.899</v>
+        <v>111.899355043358</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -21232,7 +21220,7 @@
         <v>2012</v>
       </c>
       <c r="C631" t="n">
-        <v>107.756</v>
+        <v>107.756074158579</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -21265,7 +21253,7 @@
         <v>2013</v>
       </c>
       <c r="C632" t="n">
-        <v>107.039</v>
+        <v>107.038567264134</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -21298,7 +21286,7 @@
         <v>2014</v>
       </c>
       <c r="C633" t="n">
-        <v>108.746</v>
+        <v>108.745818831037</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -21331,7 +21319,7 @@
         <v>2015</v>
       </c>
       <c r="C634" t="n">
-        <v>109.391</v>
+        <v>109.391040801705</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -21364,7 +21352,7 @@
         <v>2016</v>
       </c>
       <c r="C635" t="n">
-        <v>110.247</v>
+        <v>110.247061960011</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -21397,7 +21385,7 @@
         <v>2017</v>
       </c>
       <c r="C636" t="n">
-        <v>112.03</v>
+        <v>112.030085134191</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -21430,7 +21418,7 @@
         <v>2018</v>
       </c>
       <c r="C637" t="n">
-        <v>115.009</v>
+        <v>115.009066880916</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -21463,7 +21451,7 @@
         <v>2019</v>
       </c>
       <c r="C638" t="n">
-        <v>116.696</v>
+        <v>116.69612128516</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -21496,7 +21484,7 @@
         <v>2020</v>
       </c>
       <c r="C639" t="n">
-        <v>116.712</v>
+        <v>116.712041523767</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -21529,7 +21517,7 @@
         <v>2021</v>
       </c>
       <c r="C640" t="n">
-        <v>119</v>
+        <v>118.999806936801</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -21562,7 +21550,7 @@
         <v>2022</v>
       </c>
       <c r="C641" t="n">
-        <v>123.4</v>
+        <v>123.399528756795</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -21595,7 +21583,7 @@
         <v>2023</v>
       </c>
       <c r="C642" t="n">
-        <v>127.715</v>
+        <v>127.715490236713</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -21628,7 +21616,7 @@
         <v>2024</v>
       </c>
       <c r="C643" t="n">
-        <v>130.261</v>
+        <v>130.260997343256</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -21661,7 +21649,7 @@
         <v>2010</v>
       </c>
       <c r="C644" t="n">
-        <v>124.136</v>
+        <v>124.136203591879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -21694,7 +21682,7 @@
         <v>2011</v>
       </c>
       <c r="C645" t="n">
-        <v>136.065</v>
+        <v>136.065402099509</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -21727,7 +21715,7 @@
         <v>2012</v>
       </c>
       <c r="C646" t="n">
-        <v>151.197</v>
+        <v>151.196568013694</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -21760,7 +21748,7 @@
         <v>2013</v>
       </c>
       <c r="C647" t="n">
-        <v>146.247</v>
+        <v>146.247455268495</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -21793,7 +21781,7 @@
         <v>2014</v>
       </c>
       <c r="C648" t="n">
-        <v>144.361</v>
+        <v>144.360615678625</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -21826,7 +21814,7 @@
         <v>2015</v>
       </c>
       <c r="C649" t="n">
-        <v>144.803</v>
+        <v>144.802963084675</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -21859,7 +21847,7 @@
         <v>2016</v>
       </c>
       <c r="C650" t="n">
-        <v>144.235</v>
+        <v>144.235470787302</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -21892,7 +21880,7 @@
         <v>2017</v>
       </c>
       <c r="C651" t="n">
-        <v>144.557</v>
+        <v>144.556616126155</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -21925,7 +21913,7 @@
         <v>2018</v>
       </c>
       <c r="C652" t="n">
-        <v>145.543</v>
+        <v>145.543490183174</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -21958,7 +21946,7 @@
         <v>2019</v>
       </c>
       <c r="C653" t="n">
-        <v>147.047</v>
+        <v>147.04692867619</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -21991,7 +21979,7 @@
         <v>2020</v>
       </c>
       <c r="C654" t="n">
-        <v>144.832</v>
+        <v>144.832210121466</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -22024,7 +22012,7 @@
         <v>2021</v>
       </c>
       <c r="C655" t="n">
-        <v>148.74</v>
+        <v>148.739589817601</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -22057,7 +22045,7 @@
         <v>2022</v>
       </c>
       <c r="C656" t="n">
-        <v>152.271</v>
+        <v>152.270772859015</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -22090,7 +22078,7 @@
         <v>2023</v>
       </c>
       <c r="C657" t="n">
-        <v>150.196</v>
+        <v>150.195729068839</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -22123,7 +22111,7 @@
         <v>2024</v>
       </c>
       <c r="C658" t="n">
-        <v>151.132</v>
+        <v>151.131825017309</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -22156,7 +22144,7 @@
         <v>2010</v>
       </c>
       <c r="C659" t="n">
-        <v>91.1186</v>
+        <v>91.11857899231789</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -22189,7 +22177,7 @@
         <v>2011</v>
       </c>
       <c r="C660" t="n">
-        <v>93.85290000000001</v>
+        <v>93.8529031474159</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -22222,7 +22210,7 @@
         <v>2012</v>
       </c>
       <c r="C661" t="n">
-        <v>97.1925</v>
+        <v>97.1924631662654</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -22255,7 +22243,7 @@
         <v>2013</v>
       </c>
       <c r="C662" t="n">
-        <v>98.3479</v>
+        <v>98.34792446648299</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -22288,7 +22276,7 @@
         <v>2014</v>
       </c>
       <c r="C663" t="n">
-        <v>101.132</v>
+        <v>101.132290573498</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -22321,7 +22309,7 @@
         <v>2015</v>
       </c>
       <c r="C664" t="n">
-        <v>102.718</v>
+        <v>102.718366606519</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -22354,7 +22342,7 @@
         <v>2016</v>
       </c>
       <c r="C665" t="n">
-        <v>103.817</v>
+        <v>103.816661597799</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -22387,7 +22375,7 @@
         <v>2017</v>
       </c>
       <c r="C666" t="n">
-        <v>105.718</v>
+        <v>105.718368398783</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -22420,7 +22408,7 @@
         <v>2018</v>
       </c>
       <c r="C667" t="n">
-        <v>107.482</v>
+        <v>107.482434668386</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -22453,7 +22441,7 @@
         <v>2019</v>
       </c>
       <c r="C668" t="n">
-        <v>109.601</v>
+        <v>109.600780374596</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -22486,7 +22474,7 @@
         <v>2020</v>
       </c>
       <c r="C669" t="n">
-        <v>110.387</v>
+        <v>110.387215275645</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -22519,7 +22507,7 @@
         <v>2021</v>
       </c>
       <c r="C670" t="n">
-        <v>113.953</v>
+        <v>113.952719366702</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -22552,7 +22540,7 @@
         <v>2022</v>
       </c>
       <c r="C671" t="n">
-        <v>115.951</v>
+        <v>115.950519429629</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -22585,7 +22573,7 @@
         <v>2023</v>
       </c>
       <c r="C672" t="n">
-        <v>116.688</v>
+        <v>116.687800394775</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -22618,7 +22606,7 @@
         <v>2010</v>
       </c>
       <c r="C673" t="n">
-        <v>156.432</v>
+        <v>156.432080695834</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -22651,7 +22639,7 @@
         <v>2011</v>
       </c>
       <c r="C674" t="n">
-        <v>165.917</v>
+        <v>165.916854869706</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -22684,7 +22672,7 @@
         <v>2012</v>
       </c>
       <c r="C675" t="n">
-        <v>172.147</v>
+        <v>172.147209506663</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -22717,7 +22705,7 @@
         <v>2013</v>
       </c>
       <c r="C676" t="n">
-        <v>136.259</v>
+        <v>136.259014207069</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -22750,7 +22738,7 @@
         <v>2014</v>
       </c>
       <c r="C677" t="n">
-        <v>139.199</v>
+        <v>139.198825856641</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -22783,7 +22771,7 @@
         <v>2015</v>
       </c>
       <c r="C678" t="n">
-        <v>134.974</v>
+        <v>134.974123663686</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -22816,7 +22804,7 @@
         <v>2016</v>
       </c>
       <c r="C679" t="n">
-        <v>131.383</v>
+        <v>131.382780978293</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -22849,7 +22837,7 @@
         <v>2017</v>
       </c>
       <c r="C680" t="n">
-        <v>129.983</v>
+        <v>129.983392624641</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -22882,7 +22870,7 @@
         <v>2018</v>
       </c>
       <c r="C681" t="n">
-        <v>129.629</v>
+        <v>129.629119305202</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -22915,7 +22903,7 @@
         <v>2019</v>
       </c>
       <c r="C682" t="n">
-        <v>129.488</v>
+        <v>129.487723024493</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -22948,7 +22936,7 @@
         <v>2020</v>
       </c>
       <c r="C683" t="n">
-        <v>128.761</v>
+        <v>128.761294644181</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -22981,7 +22969,7 @@
         <v>2021</v>
       </c>
       <c r="C684" t="n">
-        <v>129.036</v>
+        <v>129.036333202492</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -23014,7 +23002,7 @@
         <v>2022</v>
       </c>
       <c r="C685" t="n">
-        <v>128.023</v>
+        <v>128.023293416281</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -23047,7 +23035,7 @@
         <v>2023</v>
       </c>
       <c r="C686" t="n">
-        <v>127.473</v>
+        <v>127.47302579722</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -23080,7 +23068,7 @@
         <v>2024</v>
       </c>
       <c r="C687" t="n">
-        <v>125.861</v>
+        <v>125.860954798649</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -23113,7 +23101,7 @@
         <v>2010</v>
       </c>
       <c r="C688" t="n">
-        <v>110.5</v>
+        <v>110.499601336489</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -23146,7 +23134,7 @@
         <v>2011</v>
       </c>
       <c r="C689" t="n">
-        <v>109.174</v>
+        <v>109.174140891708</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -23179,7 +23167,7 @@
         <v>2012</v>
       </c>
       <c r="C690" t="n">
-        <v>120.926</v>
+        <v>120.926137220412</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -23212,7 +23200,7 @@
         <v>2013</v>
       </c>
       <c r="C691" t="n">
-        <v>114.143</v>
+        <v>114.142688333026</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -23245,7 +23233,7 @@
         <v>2014</v>
       </c>
       <c r="C692" t="n">
-        <v>111.488</v>
+        <v>111.488230327161</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -23278,7 +23266,7 @@
         <v>2015</v>
       </c>
       <c r="C693" t="n">
-        <v>116.133</v>
+        <v>116.133089816996</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -23311,7 +23299,7 @@
         <v>2016</v>
       </c>
       <c r="C694" t="n">
-        <v>116.365</v>
+        <v>116.365109232942</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -23344,7 +23332,7 @@
         <v>2017</v>
       </c>
       <c r="C695" t="n">
-        <v>120.306</v>
+        <v>120.305633506681</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -23377,7 +23365,7 @@
         <v>2018</v>
       </c>
       <c r="C696" t="n">
-        <v>113.418</v>
+        <v>113.418450589721</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -23410,7 +23398,7 @@
         <v>2019</v>
       </c>
       <c r="C697" t="n">
-        <v>110.855</v>
+        <v>110.855033355177</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -23443,7 +23431,7 @@
         <v>2020</v>
       </c>
       <c r="C698" t="n">
-        <v>106.67</v>
+        <v>106.669795200072</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -23476,7 +23464,7 @@
         <v>2021</v>
       </c>
       <c r="C699" t="n">
-        <v>108.644</v>
+        <v>108.643525000707</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -23509,7 +23497,7 @@
         <v>2022</v>
       </c>
       <c r="C700" t="n">
-        <v>109.027</v>
+        <v>109.026956114201</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -23542,7 +23530,7 @@
         <v>2023</v>
       </c>
       <c r="C701" t="n">
-        <v>110.792</v>
+        <v>110.79216956747</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -23575,7 +23563,7 @@
         <v>2024</v>
       </c>
       <c r="C702" t="n">
-        <v>113.598</v>
+        <v>113.597610306796</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -23608,7 +23596,7 @@
         <v>2010</v>
       </c>
       <c r="C703" t="n">
-        <v>120.369</v>
+        <v>120.369453085535</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -23641,7 +23629,7 @@
         <v>2011</v>
       </c>
       <c r="C704" t="n">
-        <v>117.526</v>
+        <v>117.526065994308</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -23674,7 +23662,7 @@
         <v>2012</v>
       </c>
       <c r="C705" t="n">
-        <v>116.768</v>
+        <v>116.767825095297</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -23707,7 +23695,7 @@
         <v>2013</v>
       </c>
       <c r="C706" t="n">
-        <v>117.2</v>
+        <v>117.200126277309</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -23740,7 +23728,7 @@
         <v>2014</v>
       </c>
       <c r="C707" t="n">
-        <v>118.896</v>
+        <v>118.895659080821</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -23773,7 +23761,7 @@
         <v>2015</v>
       </c>
       <c r="C708" t="n">
-        <v>100.624</v>
+        <v>100.623739037612</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -23806,7 +23794,7 @@
         <v>2016</v>
       </c>
       <c r="C709" t="n">
-        <v>101.442</v>
+        <v>101.442011503556</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -23839,7 +23827,7 @@
         <v>2017</v>
       </c>
       <c r="C710" t="n">
-        <v>101.629</v>
+        <v>101.629260697653</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -23872,7 +23860,7 @@
         <v>2018</v>
       </c>
       <c r="C711" t="n">
-        <v>102.737</v>
+        <v>102.737202940663</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -23905,7 +23893,7 @@
         <v>2019</v>
       </c>
       <c r="C712" t="n">
-        <v>105.142</v>
+        <v>105.141557934591</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -23938,7 +23926,7 @@
         <v>2020</v>
       </c>
       <c r="C713" t="n">
-        <v>105.982</v>
+        <v>105.981902376717</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -23971,7 +23959,7 @@
         <v>2021</v>
       </c>
       <c r="C714" t="n">
-        <v>105.137</v>
+        <v>105.137285804787</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -24004,7 +23992,7 @@
         <v>2022</v>
       </c>
       <c r="C715" t="n">
-        <v>105.794</v>
+        <v>105.793848314995</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -24037,7 +24025,7 @@
         <v>2023</v>
       </c>
       <c r="C716" t="n">
-        <v>105.054</v>
+        <v>105.054424922699</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -24070,7 +24058,7 @@
         <v>2024</v>
       </c>
       <c r="C717" t="n">
-        <v>104.581</v>
+        <v>104.58063059269</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -24103,7 +24091,7 @@
         <v>2010</v>
       </c>
       <c r="C718" t="n">
-        <v>114.357</v>
+        <v>114.356515784318</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -24136,7 +24124,7 @@
         <v>2011</v>
       </c>
       <c r="C719" t="n">
-        <v>117.674</v>
+        <v>117.673977365337</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -24169,7 +24157,7 @@
         <v>2012</v>
       </c>
       <c r="C720" t="n">
-        <v>116.564</v>
+        <v>116.563841951798</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -24202,7 +24190,7 @@
         <v>2013</v>
       </c>
       <c r="C721" t="n">
-        <v>114.734</v>
+        <v>114.73405856983</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -24235,7 +24223,7 @@
         <v>2014</v>
       </c>
       <c r="C722" t="n">
-        <v>114.867</v>
+        <v>114.867279906758</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -24268,7 +24256,7 @@
         <v>2015</v>
       </c>
       <c r="C723" t="n">
-        <v>121.638</v>
+        <v>121.637501079209</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -24301,7 +24289,7 @@
         <v>2016</v>
       </c>
       <c r="C724" t="n">
-        <v>121.42</v>
+        <v>121.420358968335</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -24334,7 +24322,7 @@
         <v>2017</v>
       </c>
       <c r="C725" t="n">
-        <v>118.577</v>
+        <v>118.57673269471</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -24367,7 +24355,7 @@
         <v>2018</v>
       </c>
       <c r="C726" t="n">
-        <v>121.162</v>
+        <v>121.162164892591</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -24400,7 +24388,7 @@
         <v>2019</v>
       </c>
       <c r="C727" t="n">
-        <v>124.088</v>
+        <v>124.08833250929</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -24433,7 +24421,7 @@
         <v>2020</v>
       </c>
       <c r="C728" t="n">
-        <v>121.423</v>
+        <v>121.422728509042</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -24466,7 +24454,7 @@
         <v>2021</v>
       </c>
       <c r="C729" t="n">
-        <v>123.448</v>
+        <v>123.447849713072</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -24499,7 +24487,7 @@
         <v>2022</v>
       </c>
       <c r="C730" t="n">
-        <v>115.821</v>
+        <v>115.8205562749</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -24532,7 +24520,7 @@
         <v>2023</v>
       </c>
       <c r="C731" t="n">
-        <v>125.273</v>
+        <v>125.272736960305</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -24565,7 +24553,7 @@
         <v>2024</v>
       </c>
       <c r="C732" t="n">
-        <v>128.539</v>
+        <v>128.538765867661</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -24598,7 +24586,7 @@
         <v>2010</v>
       </c>
       <c r="C733" t="n">
-        <v>114.582</v>
+        <v>114.582326334034</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -24631,7 +24619,7 @@
         <v>2011</v>
       </c>
       <c r="C734" t="n">
-        <v>119.49</v>
+        <v>119.489612280253</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -24664,7 +24652,7 @@
         <v>2012</v>
       </c>
       <c r="C735" t="n">
-        <v>116.719</v>
+        <v>116.719313041118</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -24697,7 +24685,7 @@
         <v>2013</v>
       </c>
       <c r="C736" t="n">
-        <v>111.282</v>
+        <v>111.281756214292</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -24730,7 +24718,7 @@
         <v>2014</v>
       </c>
       <c r="C737" t="n">
-        <v>105.732</v>
+        <v>105.732295385283</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -24763,7 +24751,7 @@
         <v>2015</v>
       </c>
       <c r="C738" t="n">
-        <v>105.544</v>
+        <v>105.543643003646</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -24796,7 +24784,7 @@
         <v>2016</v>
       </c>
       <c r="C739" t="n">
-        <v>106.718</v>
+        <v>106.718403536951</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -24829,7 +24817,7 @@
         <v>2017</v>
       </c>
       <c r="C740" t="n">
-        <v>105.795</v>
+        <v>105.794763679153</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -24862,7 +24850,7 @@
         <v>2018</v>
       </c>
       <c r="C741" t="n">
-        <v>109.034</v>
+        <v>109.034035401906</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -24895,7 +24883,7 @@
         <v>2019</v>
       </c>
       <c r="C742" t="n">
-        <v>110.494</v>
+        <v>110.493802074789</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -24928,7 +24916,7 @@
         <v>2020</v>
       </c>
       <c r="C743" t="n">
-        <v>110.666</v>
+        <v>110.666299439701</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -24961,7 +24949,7 @@
         <v>2021</v>
       </c>
       <c r="C744" t="n">
-        <v>112.169</v>
+        <v>112.169438491978</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -24994,7 +24982,7 @@
         <v>2022</v>
       </c>
       <c r="C745" t="n">
-        <v>114.677</v>
+        <v>114.677195729643</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -25027,7 +25015,7 @@
         <v>2023</v>
       </c>
       <c r="C746" t="n">
-        <v>117.113</v>
+        <v>117.112604314708</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -25060,7 +25048,7 @@
         <v>2024</v>
       </c>
       <c r="C747" t="n">
-        <v>121.733</v>
+        <v>121.732525659138</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -25093,7 +25081,7 @@
         <v>2010</v>
       </c>
       <c r="C748" t="n">
-        <v>155.684</v>
+        <v>155.684057564253</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -25126,7 +25114,7 @@
         <v>2011</v>
       </c>
       <c r="C749" t="n">
-        <v>159.093</v>
+        <v>159.092737727414</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -25159,7 +25147,7 @@
         <v>2012</v>
       </c>
       <c r="C750" t="n">
-        <v>160.559</v>
+        <v>160.558717223582</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -25192,7 +25180,7 @@
         <v>2013</v>
       </c>
       <c r="C751" t="n">
-        <v>159.698</v>
+        <v>159.698153133449</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -25225,7 +25213,7 @@
         <v>2014</v>
       </c>
       <c r="C752" t="n">
-        <v>148.217</v>
+        <v>148.21699121216</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -25258,7 +25246,7 @@
         <v>2015</v>
       </c>
       <c r="C753" t="n">
-        <v>144.764</v>
+        <v>144.763979440074</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -25291,7 +25279,7 @@
         <v>2016</v>
       </c>
       <c r="C754" t="n">
-        <v>142.127</v>
+        <v>142.127307324616</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -25324,7 +25312,7 @@
         <v>2017</v>
       </c>
       <c r="C755" t="n">
-        <v>138.882</v>
+        <v>138.882433107903</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -25357,7 +25345,7 @@
         <v>2018</v>
       </c>
       <c r="C756" t="n">
-        <v>138.265</v>
+        <v>138.264671531909</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -25390,7 +25378,7 @@
         <v>2019</v>
       </c>
       <c r="C757" t="n">
-        <v>132.181</v>
+        <v>132.181234381376</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -25423,7 +25411,7 @@
         <v>2020</v>
       </c>
       <c r="C758" t="n">
-        <v>129.49</v>
+        <v>129.49000571147</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -25456,7 +25444,7 @@
         <v>2021</v>
       </c>
       <c r="C759" t="n">
-        <v>130.781</v>
+        <v>130.781488497698</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -25489,7 +25477,7 @@
         <v>2022</v>
       </c>
       <c r="C760" t="n">
-        <v>131.674</v>
+        <v>131.673965640047</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -25522,7 +25510,7 @@
         <v>2023</v>
       </c>
       <c r="C761" t="n">
-        <v>131.872</v>
+        <v>131.871674517747</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -25555,7 +25543,7 @@
         <v>2024</v>
       </c>
       <c r="C762" t="n">
-        <v>132.575</v>
+        <v>132.575141676252</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -25588,7 +25576,7 @@
         <v>2010</v>
       </c>
       <c r="C763" t="n">
-        <v>103.123</v>
+        <v>103.123305579196</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -25621,7 +25609,7 @@
         <v>2011</v>
       </c>
       <c r="C764" t="n">
-        <v>107.135</v>
+        <v>107.134899495633</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -25654,7 +25642,7 @@
         <v>2012</v>
       </c>
       <c r="C765" t="n">
-        <v>108.99</v>
+        <v>108.989828987516</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -25687,7 +25675,7 @@
         <v>2013</v>
       </c>
       <c r="C766" t="n">
-        <v>105.538</v>
+        <v>105.53780299895</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -25720,7 +25708,7 @@
         <v>2014</v>
       </c>
       <c r="C767" t="n">
-        <v>105.461</v>
+        <v>105.460883393918</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -25753,7 +25741,7 @@
         <v>2015</v>
       </c>
       <c r="C768" t="n">
-        <v>104.243</v>
+        <v>104.242903808134</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -25786,7 +25774,7 @@
         <v>2016</v>
       </c>
       <c r="C769" t="n">
-        <v>102.558</v>
+        <v>102.558386941167</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -25819,7 +25807,7 @@
         <v>2017</v>
       </c>
       <c r="C770" t="n">
-        <v>101.842</v>
+        <v>101.842124574945</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -25852,7 +25840,7 @@
         <v>2018</v>
       </c>
       <c r="C771" t="n">
-        <v>102.03</v>
+        <v>102.030494877842</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -25885,7 +25873,7 @@
         <v>2019</v>
       </c>
       <c r="C772" t="n">
-        <v>104.598</v>
+        <v>104.597515228061</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -25918,7 +25906,7 @@
         <v>2020</v>
       </c>
       <c r="C773" t="n">
-        <v>105.046</v>
+        <v>105.045612677382</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -25951,7 +25939,7 @@
         <v>2021</v>
       </c>
       <c r="C774" t="n">
-        <v>106.87</v>
+        <v>106.86972424373</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -25984,7 +25972,7 @@
         <v>2022</v>
       </c>
       <c r="C775" t="n">
-        <v>110.609</v>
+        <v>110.608851322579</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -26017,7 +26005,7 @@
         <v>2023</v>
       </c>
       <c r="C776" t="n">
-        <v>110.798</v>
+        <v>110.798344311602</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -26050,7 +26038,7 @@
         <v>2024</v>
       </c>
       <c r="C777" t="n">
-        <v>112.639</v>
+        <v>112.638817343502</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -26083,7 +26071,7 @@
         <v>2010</v>
       </c>
       <c r="C778" t="n">
-        <v>157.89</v>
+        <v>157.889641413685</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -26116,7 +26104,7 @@
         <v>2011</v>
       </c>
       <c r="C779" t="n">
-        <v>163.043</v>
+        <v>163.043370593157</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -26149,7 +26137,7 @@
         <v>2012</v>
       </c>
       <c r="C780" t="n">
-        <v>167.226</v>
+        <v>167.226065135398</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -26182,7 +26170,7 @@
         <v>2013</v>
       </c>
       <c r="C781" t="n">
-        <v>154.341</v>
+        <v>154.341459457267</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -26215,7 +26203,7 @@
         <v>2014</v>
       </c>
       <c r="C782" t="n">
-        <v>145.494</v>
+        <v>145.49429149643</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -26248,7 +26236,7 @@
         <v>2015</v>
       </c>
       <c r="C783" t="n">
-        <v>143.991</v>
+        <v>143.991494147494</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -26281,7 +26269,7 @@
         <v>2016</v>
       </c>
       <c r="C784" t="n">
-        <v>146.55</v>
+        <v>146.550393676088</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -26314,7 +26302,7 @@
         <v>2017</v>
       </c>
       <c r="C785" t="n">
-        <v>154.148</v>
+        <v>154.147985747777</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -26347,7 +26335,7 @@
         <v>2018</v>
       </c>
       <c r="C786" t="n">
-        <v>134.334</v>
+        <v>134.333614750945</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -26380,7 +26368,7 @@
         <v>2019</v>
       </c>
       <c r="C787" t="n">
-        <v>132.529</v>
+        <v>132.528841977519</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -26413,7 +26401,7 @@
         <v>2020</v>
       </c>
       <c r="C788" t="n">
-        <v>131.341</v>
+        <v>131.341332336588</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -26446,7 +26434,7 @@
         <v>2021</v>
       </c>
       <c r="C789" t="n">
-        <v>133.357</v>
+        <v>133.357273318046</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -26479,7 +26467,7 @@
         <v>2022</v>
       </c>
       <c r="C790" t="n">
-        <v>135.834</v>
+        <v>135.834150715729</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -26512,7 +26500,7 @@
         <v>2023</v>
       </c>
       <c r="C791" t="n">
-        <v>137.204</v>
+        <v>137.203719983084</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -26545,7 +26533,7 @@
         <v>2024</v>
       </c>
       <c r="C792" t="n">
-        <v>138.729</v>
+        <v>138.728835196967</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -26578,7 +26566,7 @@
         <v>2010</v>
       </c>
       <c r="C793" t="n">
-        <v>143.277</v>
+        <v>143.276640192349</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -26611,7 +26599,7 @@
         <v>2011</v>
       </c>
       <c r="C794" t="n">
-        <v>147.512</v>
+        <v>147.511878499915</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -26644,7 +26632,7 @@
         <v>2012</v>
       </c>
       <c r="C795" t="n">
-        <v>143.388</v>
+        <v>143.387946442865</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -26677,7 +26665,7 @@
         <v>2013</v>
       </c>
       <c r="C796" t="n">
-        <v>145.093</v>
+        <v>145.093438163702</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -26710,7 +26698,7 @@
         <v>2014</v>
       </c>
       <c r="C797" t="n">
-        <v>144.244</v>
+        <v>144.244165248014</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -26743,7 +26731,7 @@
         <v>2015</v>
       </c>
       <c r="C798" t="n">
-        <v>141.659</v>
+        <v>141.659175188223</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -26776,7 +26764,7 @@
         <v>2016</v>
       </c>
       <c r="C799" t="n">
-        <v>130.933</v>
+        <v>130.932672500368</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -26809,7 +26797,7 @@
         <v>2017</v>
       </c>
       <c r="C800" t="n">
-        <v>133.111</v>
+        <v>133.110922975046</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -26842,7 +26830,7 @@
         <v>2018</v>
       </c>
       <c r="C801" t="n">
-        <v>131.327</v>
+        <v>131.326868398506</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -26875,7 +26863,7 @@
         <v>2019</v>
       </c>
       <c r="C802" t="n">
-        <v>131.87</v>
+        <v>131.870169616698</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -26908,7 +26896,7 @@
         <v>2020</v>
       </c>
       <c r="C803" t="n">
-        <v>132.909</v>
+        <v>132.908973559976</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -26941,7 +26929,7 @@
         <v>2021</v>
       </c>
       <c r="C804" t="n">
-        <v>136.871</v>
+        <v>136.87108956478</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -26974,7 +26962,7 @@
         <v>2022</v>
       </c>
       <c r="C805" t="n">
-        <v>139.651</v>
+        <v>139.651285065505</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -27007,7 +26995,7 @@
         <v>2023</v>
       </c>
       <c r="C806" t="n">
-        <v>144.475</v>
+        <v>144.474949556306</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -27040,7 +27028,7 @@
         <v>2010</v>
       </c>
       <c r="C807" t="n">
-        <v>109.928</v>
+        <v>109.927825454005</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -27073,7 +27061,7 @@
         <v>2011</v>
       </c>
       <c r="C808" t="n">
-        <v>112.091</v>
+        <v>112.090589002306</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -27106,7 +27094,7 @@
         <v>2012</v>
       </c>
       <c r="C809" t="n">
-        <v>129.305</v>
+        <v>129.304547798055</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -27139,7 +27127,7 @@
         <v>2013</v>
       </c>
       <c r="C810" t="n">
-        <v>127.073</v>
+        <v>127.073387613574</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -27172,7 +27160,7 @@
         <v>2014</v>
       </c>
       <c r="C811" t="n">
-        <v>119.55</v>
+        <v>119.549742772481</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -27205,7 +27193,7 @@
         <v>2015</v>
       </c>
       <c r="C812" t="n">
-        <v>130.949</v>
+        <v>130.949148754694</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -27238,7 +27226,7 @@
         <v>2016</v>
       </c>
       <c r="C813" t="n">
-        <v>135.227</v>
+        <v>135.227462327724</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -27271,7 +27259,7 @@
         <v>2017</v>
       </c>
       <c r="C814" t="n">
-        <v>126.847</v>
+        <v>126.846989128969</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -27304,7 +27292,7 @@
         <v>2018</v>
       </c>
       <c r="C815" t="n">
-        <v>107.397</v>
+        <v>107.397431401316</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -27337,7 +27325,7 @@
         <v>2019</v>
       </c>
       <c r="C816" t="n">
-        <v>108.222</v>
+        <v>108.221910991332</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -27370,7 +27358,7 @@
         <v>2020</v>
       </c>
       <c r="C817" t="n">
-        <v>107.902</v>
+        <v>107.902487108935</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -27403,7 +27391,7 @@
         <v>2021</v>
       </c>
       <c r="C818" t="n">
-        <v>114.645</v>
+        <v>114.644670333429</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -27436,7 +27424,7 @@
         <v>2022</v>
       </c>
       <c r="C819" t="n">
-        <v>115.203</v>
+        <v>115.202627450543</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -27469,7 +27457,7 @@
         <v>2023</v>
       </c>
       <c r="C820" t="n">
-        <v>119.91</v>
+        <v>119.909944560018</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -27502,7 +27490,7 @@
         <v>2024</v>
       </c>
       <c r="C821" t="n">
-        <v>121.262</v>
+        <v>121.262202363304</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -27535,7 +27523,7 @@
         <v>2010</v>
       </c>
       <c r="C822" t="n">
-        <v>107.791</v>
+        <v>107.790825054241</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -27568,7 +27556,7 @@
         <v>2011</v>
       </c>
       <c r="C823" t="n">
-        <v>122.872</v>
+        <v>122.871784244091</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -27601,7 +27589,7 @@
         <v>2012</v>
       </c>
       <c r="C824" t="n">
-        <v>124.757</v>
+        <v>124.757214417819</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -27634,7 +27622,7 @@
         <v>2013</v>
       </c>
       <c r="C825" t="n">
-        <v>129.922</v>
+        <v>129.921671505793</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -27667,7 +27655,7 @@
         <v>2014</v>
       </c>
       <c r="C826" t="n">
-        <v>125.719</v>
+        <v>125.718724466898</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -27700,7 +27688,7 @@
         <v>2015</v>
       </c>
       <c r="C827" t="n">
-        <v>117.794</v>
+        <v>117.794018171562</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -27733,7 +27721,7 @@
         <v>2016</v>
       </c>
       <c r="C828" t="n">
-        <v>128.599</v>
+        <v>128.59869659476</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -27766,7 +27754,7 @@
         <v>2017</v>
       </c>
       <c r="C829" t="n">
-        <v>129.249</v>
+        <v>129.249073523943</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -27799,7 +27787,7 @@
         <v>2018</v>
       </c>
       <c r="C830" t="n">
-        <v>127.094</v>
+        <v>127.093763801237</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -27832,7 +27820,7 @@
         <v>2019</v>
       </c>
       <c r="C831" t="n">
-        <v>125.866</v>
+        <v>125.866492068688</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -27865,7 +27853,7 @@
         <v>2020</v>
       </c>
       <c r="C832" t="n">
-        <v>122.176</v>
+        <v>122.175694268893</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -27898,7 +27886,7 @@
         <v>2021</v>
       </c>
       <c r="C833" t="n">
-        <v>123.941</v>
+        <v>123.941408455002</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -27931,7 +27919,7 @@
         <v>2022</v>
       </c>
       <c r="C834" t="n">
-        <v>132.861</v>
+        <v>132.861156549134</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -27964,7 +27952,7 @@
         <v>2023</v>
       </c>
       <c r="C835" t="n">
-        <v>140.594</v>
+        <v>140.59359496844</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -27997,7 +27985,7 @@
         <v>2024</v>
       </c>
       <c r="C836" t="n">
-        <v>142.07</v>
+        <v>142.070062100751</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -28030,7 +28018,7 @@
         <v>2010</v>
       </c>
       <c r="C837" t="n">
-        <v>123.249</v>
+        <v>123.248926095995</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -28063,7 +28051,7 @@
         <v>2011</v>
       </c>
       <c r="C838" t="n">
-        <v>131.28</v>
+        <v>131.279778766286</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -28096,7 +28084,7 @@
         <v>2012</v>
       </c>
       <c r="C839" t="n">
-        <v>141.41</v>
+        <v>141.409735570098</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -28129,7 +28117,7 @@
         <v>2013</v>
       </c>
       <c r="C840" t="n">
-        <v>148.912</v>
+        <v>148.912446350899</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -28162,7 +28150,7 @@
         <v>2014</v>
       </c>
       <c r="C841" t="n">
-        <v>148.713</v>
+        <v>148.713283559361</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -28195,7 +28183,7 @@
         <v>2015</v>
       </c>
       <c r="C842" t="n">
-        <v>142.52</v>
+        <v>142.520207198425</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -28228,7 +28216,7 @@
         <v>2016</v>
       </c>
       <c r="C843" t="n">
-        <v>138.519</v>
+        <v>138.518696718641</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -28261,7 +28249,7 @@
         <v>2017</v>
       </c>
       <c r="C844" t="n">
-        <v>131.901</v>
+        <v>131.901471911132</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -28294,7 +28282,7 @@
         <v>2018</v>
       </c>
       <c r="C845" t="n">
-        <v>126.266</v>
+        <v>126.266191655563</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -28327,7 +28315,7 @@
         <v>2019</v>
       </c>
       <c r="C846" t="n">
-        <v>126.597</v>
+        <v>126.597314882311</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -28360,7 +28348,7 @@
         <v>2020</v>
       </c>
       <c r="C847" t="n">
-        <v>129.288</v>
+        <v>129.288487295019</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -28393,7 +28381,7 @@
         <v>2021</v>
       </c>
       <c r="C848" t="n">
-        <v>132.987</v>
+        <v>132.987203939653</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -28426,7 +28414,7 @@
         <v>2022</v>
       </c>
       <c r="C849" t="n">
-        <v>137.002</v>
+        <v>137.002148115476</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -28459,7 +28447,7 @@
         <v>2023</v>
       </c>
       <c r="C850" t="n">
-        <v>135.146</v>
+        <v>135.146301442691</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -28492,7 +28480,7 @@
         <v>2024</v>
       </c>
       <c r="C851" t="n">
-        <v>138.016</v>
+        <v>138.016156588197</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -28525,7 +28513,7 @@
         <v>2010</v>
       </c>
       <c r="C852" t="n">
-        <v>115.425</v>
+        <v>115.42460954412</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -28558,7 +28546,7 @@
         <v>2011</v>
       </c>
       <c r="C853" t="n">
-        <v>116.837</v>
+        <v>116.837494027689</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -28591,7 +28579,7 @@
         <v>2012</v>
       </c>
       <c r="C854" t="n">
-        <v>113.359</v>
+        <v>113.358650832529</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -28624,7 +28612,7 @@
         <v>2013</v>
       </c>
       <c r="C855" t="n">
-        <v>114.655</v>
+        <v>114.655300508744</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -28657,7 +28645,7 @@
         <v>2014</v>
       </c>
       <c r="C856" t="n">
-        <v>114.313</v>
+        <v>114.312891767686</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -28690,7 +28678,7 @@
         <v>2015</v>
       </c>
       <c r="C857" t="n">
-        <v>112.964</v>
+        <v>112.964237082806</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -28723,7 +28711,7 @@
         <v>2016</v>
       </c>
       <c r="C858" t="n">
-        <v>111.847</v>
+        <v>111.846790353179</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -28756,7 +28744,7 @@
         <v>2017</v>
       </c>
       <c r="C859" t="n">
-        <v>113.874</v>
+        <v>113.873619619075</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -28789,7 +28777,7 @@
         <v>2018</v>
       </c>
       <c r="C860" t="n">
-        <v>114.859</v>
+        <v>114.858523480989</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -28822,7 +28810,7 @@
         <v>2019</v>
       </c>
       <c r="C861" t="n">
-        <v>115.146</v>
+        <v>115.145564535894</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -28855,7 +28843,7 @@
         <v>2020</v>
       </c>
       <c r="C862" t="n">
-        <v>114.276</v>
+        <v>114.276382888841</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -28888,7 +28876,7 @@
         <v>2021</v>
       </c>
       <c r="C863" t="n">
-        <v>119.769</v>
+        <v>119.768700781718</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -28921,7 +28909,7 @@
         <v>2022</v>
       </c>
       <c r="C864" t="n">
-        <v>122.801</v>
+        <v>122.80130896654</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -28954,7 +28942,7 @@
         <v>2023</v>
       </c>
       <c r="C865" t="n">
-        <v>123.002</v>
+        <v>123.001507659381</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -28987,7 +28975,7 @@
         <v>2024</v>
       </c>
       <c r="C866" t="n">
-        <v>124.13</v>
+        <v>124.129981203404</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -29020,7 +29008,7 @@
         <v>2010</v>
       </c>
       <c r="C867" t="n">
-        <v>119.221</v>
+        <v>119.221396188263</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -29053,7 +29041,7 @@
         <v>2011</v>
       </c>
       <c r="C868" t="n">
-        <v>115.472</v>
+        <v>115.471784331445</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -29086,7 +29074,7 @@
         <v>2012</v>
       </c>
       <c r="C869" t="n">
-        <v>113.302</v>
+        <v>113.302350795587</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -29119,7 +29107,7 @@
         <v>2013</v>
       </c>
       <c r="C870" t="n">
-        <v>114.191</v>
+        <v>114.190750190364</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -29152,7 +29140,7 @@
         <v>2014</v>
       </c>
       <c r="C871" t="n">
-        <v>114.783</v>
+        <v>114.782653636732</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -29185,7 +29173,7 @@
         <v>2015</v>
       </c>
       <c r="C872" t="n">
-        <v>116.35</v>
+        <v>116.350349219635</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -29218,7 +29206,7 @@
         <v>2016</v>
       </c>
       <c r="C873" t="n">
-        <v>115.791</v>
+        <v>115.790771839543</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -29251,7 +29239,7 @@
         <v>2017</v>
       </c>
       <c r="C874" t="n">
-        <v>113.767</v>
+        <v>113.76679260075</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -29284,7 +29272,7 @@
         <v>2018</v>
       </c>
       <c r="C875" t="n">
-        <v>115.492</v>
+        <v>115.492130982384</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -29317,7 +29305,7 @@
         <v>2019</v>
       </c>
       <c r="C876" t="n">
-        <v>116.252</v>
+        <v>116.252345583749</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -29350,7 +29338,7 @@
         <v>2020</v>
       </c>
       <c r="C877" t="n">
-        <v>116.478</v>
+        <v>116.478206049988</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -29383,7 +29371,7 @@
         <v>2021</v>
       </c>
       <c r="C878" t="n">
-        <v>119.123</v>
+        <v>119.123068432356</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -29416,7 +29404,7 @@
         <v>2022</v>
       </c>
       <c r="C879" t="n">
-        <v>121.142</v>
+        <v>121.14194294167</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -29449,7 +29437,7 @@
         <v>2023</v>
       </c>
       <c r="C880" t="n">
-        <v>123.252</v>
+        <v>123.252482585042</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -29482,7 +29470,7 @@
         <v>2024</v>
       </c>
       <c r="C881" t="n">
-        <v>119.805</v>
+        <v>119.804862328273</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -29515,7 +29503,7 @@
         <v>2010</v>
       </c>
       <c r="C882" t="n">
-        <v>117.212</v>
+        <v>117.211932910169</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -29548,7 +29536,7 @@
         <v>2011</v>
       </c>
       <c r="C883" t="n">
-        <v>121.219</v>
+        <v>121.218520944341</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -29581,7 +29569,7 @@
         <v>2012</v>
       </c>
       <c r="C884" t="n">
-        <v>124.465</v>
+        <v>124.465204900222</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -29614,7 +29602,7 @@
         <v>2013</v>
       </c>
       <c r="C885" t="n">
-        <v>125.142</v>
+        <v>125.141584605994</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -29647,7 +29635,7 @@
         <v>2014</v>
       </c>
       <c r="C886" t="n">
-        <v>126.98</v>
+        <v>126.980024510044</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -29680,7 +29668,7 @@
         <v>2015</v>
       </c>
       <c r="C887" t="n">
-        <v>128.974</v>
+        <v>128.974452830716</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -29713,7 +29701,7 @@
         <v>2016</v>
       </c>
       <c r="C888" t="n">
-        <v>126.402</v>
+        <v>126.401633330915</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -29746,7 +29734,7 @@
         <v>2017</v>
       </c>
       <c r="C889" t="n">
-        <v>124.473</v>
+        <v>124.472904877796</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -29779,7 +29767,7 @@
         <v>2018</v>
       </c>
       <c r="C890" t="n">
-        <v>124.086</v>
+        <v>124.086284526267</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -29812,7 +29800,7 @@
         <v>2019</v>
       </c>
       <c r="C891" t="n">
-        <v>125.457</v>
+        <v>125.456729050381</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -29845,7 +29833,7 @@
         <v>2020</v>
       </c>
       <c r="C892" t="n">
-        <v>123.549</v>
+        <v>123.548656971054</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -29878,7 +29866,7 @@
         <v>2021</v>
       </c>
       <c r="C893" t="n">
-        <v>124.961</v>
+        <v>124.96149481991</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -29911,7 +29899,7 @@
         <v>2022</v>
       </c>
       <c r="C894" t="n">
-        <v>140.782</v>
+        <v>140.781664517726</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -29944,7 +29932,7 @@
         <v>2023</v>
       </c>
       <c r="C895" t="n">
-        <v>140.266</v>
+        <v>140.265691285045</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -29977,7 +29965,7 @@
         <v>2024</v>
       </c>
       <c r="C896" t="n">
-        <v>140.687</v>
+        <v>140.686673016562</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -30010,7 +29998,7 @@
         <v>2010</v>
       </c>
       <c r="C897" t="n">
-        <v>103.783</v>
+        <v>103.782526953769</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -30043,7 +30031,7 @@
         <v>2011</v>
       </c>
       <c r="C898" t="n">
-        <v>105.845</v>
+        <v>105.844580545528</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -30076,7 +30064,7 @@
         <v>2012</v>
       </c>
       <c r="C899" t="n">
-        <v>109.148</v>
+        <v>109.148058194505</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -30109,7 +30097,7 @@
         <v>2013</v>
       </c>
       <c r="C900" t="n">
-        <v>111.045</v>
+        <v>111.044907196462</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -30142,7 +30130,7 @@
         <v>2014</v>
       </c>
       <c r="C901" t="n">
-        <v>113.019</v>
+        <v>113.019086174171</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -30175,7 +30163,7 @@
         <v>2015</v>
       </c>
       <c r="C902" t="n">
-        <v>114.271</v>
+        <v>114.271192414174</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -30208,7 +30196,7 @@
         <v>2016</v>
       </c>
       <c r="C903" t="n">
-        <v>115.736</v>
+        <v>115.736307790972</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -30241,7 +30229,7 @@
         <v>2017</v>
       </c>
       <c r="C904" t="n">
-        <v>118.462</v>
+        <v>118.461993493049</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -30274,7 +30262,7 @@
         <v>2018</v>
       </c>
       <c r="C905" t="n">
-        <v>119.153</v>
+        <v>119.153401263409</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -30307,7 +30295,7 @@
         <v>2019</v>
       </c>
       <c r="C906" t="n">
-        <v>120.569</v>
+        <v>120.568876746571</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -30340,7 +30328,7 @@
         <v>2020</v>
       </c>
       <c r="C907" t="n">
-        <v>121.331</v>
+        <v>121.331428226248</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -30373,7 +30361,7 @@
         <v>2021</v>
       </c>
       <c r="C908" t="n">
-        <v>123.363</v>
+        <v>123.362924143622</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -30406,7 +30394,7 @@
         <v>2022</v>
       </c>
       <c r="C909" t="n">
-        <v>126.459</v>
+        <v>126.45918075971</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -30439,7 +30427,7 @@
         <v>2023</v>
       </c>
       <c r="C910" t="n">
-        <v>129.228</v>
+        <v>129.227963043737</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -30472,7 +30460,7 @@
         <v>2024</v>
       </c>
       <c r="C911" t="n">
-        <v>130.861</v>
+        <v>130.86090177123</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -30505,7 +30493,7 @@
         <v>2010</v>
       </c>
       <c r="C912" t="n">
-        <v>123.605</v>
+        <v>123.605282283555</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -30538,7 +30526,7 @@
         <v>2011</v>
       </c>
       <c r="C913" t="n">
-        <v>125.46</v>
+        <v>125.460303933748</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -30571,7 +30559,7 @@
         <v>2012</v>
       </c>
       <c r="C914" t="n">
-        <v>128.69</v>
+        <v>128.69010077246</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -30604,7 +30592,7 @@
         <v>2013</v>
       </c>
       <c r="C915" t="n">
-        <v>130.521</v>
+        <v>130.521237278882</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -30637,7 +30625,7 @@
         <v>2014</v>
       </c>
       <c r="C916" t="n">
-        <v>132.289</v>
+        <v>132.288685248373</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -30670,7 +30658,7 @@
         <v>2015</v>
       </c>
       <c r="C917" t="n">
-        <v>118.34</v>
+        <v>118.339820565816</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -30703,7 +30691,7 @@
         <v>2016</v>
       </c>
       <c r="C918" t="n">
-        <v>118.544</v>
+        <v>118.544499080322</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -30736,7 +30724,7 @@
         <v>2017</v>
       </c>
       <c r="C919" t="n">
-        <v>119.874</v>
+        <v>119.874291148129</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -30769,7 +30757,7 @@
         <v>2018</v>
       </c>
       <c r="C920" t="n">
-        <v>120.432</v>
+        <v>120.431679514249</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -30802,7 +30790,7 @@
         <v>2019</v>
       </c>
       <c r="C921" t="n">
-        <v>124.126</v>
+        <v>124.126150238634</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -30835,7 +30823,7 @@
         <v>2020</v>
       </c>
       <c r="C922" t="n">
-        <v>123.219</v>
+        <v>123.219460160155</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -30868,7 +30856,7 @@
         <v>2021</v>
       </c>
       <c r="C923" t="n">
-        <v>126.173</v>
+        <v>126.173145654465</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -30901,7 +30889,7 @@
         <v>2022</v>
       </c>
       <c r="C924" t="n">
-        <v>128.105</v>
+        <v>128.105295003482</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -30934,7 +30922,7 @@
         <v>2023</v>
       </c>
       <c r="C925" t="n">
-        <v>126.005</v>
+        <v>126.004753501387</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -30967,7 +30955,7 @@
         <v>2024</v>
       </c>
       <c r="C926" t="n">
-        <v>126.6</v>
+        <v>126.600163061009</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -31000,7 +30988,7 @@
         <v>2010</v>
       </c>
       <c r="C927" t="n">
-        <v>117.768</v>
+        <v>117.767819669863</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -31033,7 +31021,7 @@
         <v>2011</v>
       </c>
       <c r="C928" t="n">
-        <v>121.942</v>
+        <v>121.941606633464</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -31066,7 +31054,7 @@
         <v>2012</v>
       </c>
       <c r="C929" t="n">
-        <v>130.859</v>
+        <v>130.859020572585</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -31099,7 +31087,7 @@
         <v>2013</v>
       </c>
       <c r="C930" t="n">
-        <v>138.441</v>
+        <v>138.441124320457</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -31132,7 +31120,7 @@
         <v>2014</v>
       </c>
       <c r="C931" t="n">
-        <v>144.279</v>
+        <v>144.278847394403</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -31165,7 +31153,7 @@
         <v>2015</v>
       </c>
       <c r="C932" t="n">
-        <v>142.003</v>
+        <v>142.003037907188</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -31198,7 +31186,7 @@
         <v>2016</v>
       </c>
       <c r="C933" t="n">
-        <v>133.169</v>
+        <v>133.168953931474</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -31231,7 +31219,7 @@
         <v>2017</v>
       </c>
       <c r="C934" t="n">
-        <v>131.357</v>
+        <v>131.356511508927</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -31264,7 +31252,7 @@
         <v>2018</v>
       </c>
       <c r="C935" t="n">
-        <v>127.754</v>
+        <v>127.753861022152</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -31297,7 +31285,7 @@
         <v>2019</v>
       </c>
       <c r="C936" t="n">
-        <v>130.629</v>
+        <v>130.629436256062</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -31330,7 +31318,7 @@
         <v>2020</v>
       </c>
       <c r="C937" t="n">
-        <v>129.341</v>
+        <v>129.341230786476</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -31363,7 +31351,7 @@
         <v>2021</v>
       </c>
       <c r="C938" t="n">
-        <v>135.026</v>
+        <v>135.025688989835</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -31396,7 +31384,7 @@
         <v>2022</v>
       </c>
       <c r="C939" t="n">
-        <v>120.261</v>
+        <v>120.261144906234</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -31429,7 +31417,7 @@
         <v>2023</v>
       </c>
       <c r="C940" t="n">
-        <v>133.38</v>
+        <v>133.38012811971</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -31462,7 +31450,7 @@
         <v>2010</v>
       </c>
       <c r="C941" t="n">
-        <v>70.2257</v>
+        <v>70.22570534296329</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -31495,7 +31483,7 @@
         <v>2011</v>
       </c>
       <c r="C942" t="n">
-        <v>90.44199999999999</v>
+        <v>90.4419573908726</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -31528,7 +31516,7 @@
         <v>2012</v>
       </c>
       <c r="C943" t="n">
-        <v>102.919</v>
+        <v>102.918975508711</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -31561,7 +31549,7 @@
         <v>2013</v>
       </c>
       <c r="C944" t="n">
-        <v>108.452</v>
+        <v>108.451690919044</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -31594,7 +31582,7 @@
         <v>2014</v>
       </c>
       <c r="C945" t="n">
-        <v>111.829</v>
+        <v>111.829207986696</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -31627,7 +31615,7 @@
         <v>2015</v>
       </c>
       <c r="C946" t="n">
-        <v>112.959</v>
+        <v>112.958678058046</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -31660,7 +31648,7 @@
         <v>2016</v>
       </c>
       <c r="C947" t="n">
-        <v>117.008</v>
+        <v>117.008370513998</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -31693,7 +31681,7 @@
         <v>2017</v>
       </c>
       <c r="C948" t="n">
-        <v>117.321</v>
+        <v>117.321043357799</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -31726,7 +31714,7 @@
         <v>2018</v>
       </c>
       <c r="C949" t="n">
-        <v>115.32</v>
+        <v>115.31999925169</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -31759,7 +31747,7 @@
         <v>2019</v>
       </c>
       <c r="C950" t="n">
-        <v>116.105</v>
+        <v>116.105189229966</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -31792,7 +31780,7 @@
         <v>2020</v>
       </c>
       <c r="C951" t="n">
-        <v>111.445</v>
+        <v>111.444672775453</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -31825,7 +31813,7 @@
         <v>2021</v>
       </c>
       <c r="C952" t="n">
-        <v>128.984</v>
+        <v>128.983642317657</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -31858,7 +31846,7 @@
         <v>2022</v>
       </c>
       <c r="C953" t="n">
-        <v>137.183</v>
+        <v>137.182551887592</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -31891,7 +31879,7 @@
         <v>2023</v>
       </c>
       <c r="C954" t="n">
-        <v>129.546</v>
+        <v>129.546081439289</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -31924,7 +31912,7 @@
         <v>2024</v>
       </c>
       <c r="C955" t="n">
-        <v>120.083</v>
+        <v>120.083487069521</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -31957,7 +31945,7 @@
         <v>2010</v>
       </c>
       <c r="C956" t="n">
-        <v>102.113</v>
+        <v>102.112900017326</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -31990,7 +31978,7 @@
         <v>2011</v>
       </c>
       <c r="C957" t="n">
-        <v>114.517</v>
+        <v>114.516931163867</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -32023,7 +32011,7 @@
         <v>2012</v>
       </c>
       <c r="C958" t="n">
-        <v>122.384</v>
+        <v>122.384147980521</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -32056,7 +32044,7 @@
         <v>2013</v>
       </c>
       <c r="C959" t="n">
-        <v>131.083</v>
+        <v>131.083096511666</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -32089,7 +32077,7 @@
         <v>2014</v>
       </c>
       <c r="C960" t="n">
-        <v>142.391</v>
+        <v>142.390867606876</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -32122,7 +32110,7 @@
         <v>2015</v>
       </c>
       <c r="C961" t="n">
-        <v>146.396</v>
+        <v>146.396495596946</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -32155,7 +32143,7 @@
         <v>2016</v>
       </c>
       <c r="C962" t="n">
-        <v>145.881</v>
+        <v>145.88058671059</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -32188,7 +32176,7 @@
         <v>2017</v>
       </c>
       <c r="C963" t="n">
-        <v>145.072</v>
+        <v>145.072490171662</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -32221,7 +32209,7 @@
         <v>2018</v>
       </c>
       <c r="C964" t="n">
-        <v>143.858</v>
+        <v>143.858127681082</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -32254,7 +32242,7 @@
         <v>2019</v>
       </c>
       <c r="C965" t="n">
-        <v>141.755</v>
+        <v>141.755414275788</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -32287,7 +32275,7 @@
         <v>2020</v>
       </c>
       <c r="C966" t="n">
-        <v>134.366</v>
+        <v>134.366007864735</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -32320,7 +32308,7 @@
         <v>2021</v>
       </c>
       <c r="C967" t="n">
-        <v>146.566</v>
+        <v>146.566472682371</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -32353,7 +32341,7 @@
         <v>2022</v>
       </c>
       <c r="C968" t="n">
-        <v>154.014</v>
+        <v>154.013561773213</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -32386,7 +32374,7 @@
         <v>2023</v>
       </c>
       <c r="C969" t="n">
-        <v>155.25</v>
+        <v>155.249965068869</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -32419,7 +32407,7 @@
         <v>2024</v>
       </c>
       <c r="C970" t="n">
-        <v>161.202</v>
+        <v>161.201784818537</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -32452,7 +32440,7 @@
         <v>2010</v>
       </c>
       <c r="C971" t="n">
-        <v>109.888</v>
+        <v>109.888273989767</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -32485,7 +32473,7 @@
         <v>2011</v>
       </c>
       <c r="C972" t="n">
-        <v>110.836</v>
+        <v>110.836202084841</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -32518,7 +32506,7 @@
         <v>2012</v>
       </c>
       <c r="C973" t="n">
-        <v>112.759</v>
+        <v>112.758768895687</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -32551,7 +32539,7 @@
         <v>2013</v>
       </c>
       <c r="C974" t="n">
-        <v>114.749</v>
+        <v>114.749126777911</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -32584,7 +32572,7 @@
         <v>2014</v>
       </c>
       <c r="C975" t="n">
-        <v>117.781</v>
+        <v>117.780685215586</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -32617,7 +32605,7 @@
         <v>2015</v>
       </c>
       <c r="C976" t="n">
-        <v>123.159</v>
+        <v>123.158867497202</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -32650,7 +32638,7 @@
         <v>2016</v>
       </c>
       <c r="C977" t="n">
-        <v>128.792</v>
+        <v>128.792489910653</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -32683,7 +32671,7 @@
         <v>2017</v>
       </c>
       <c r="C978" t="n">
-        <v>130.945</v>
+        <v>130.944551759663</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -32716,7 +32704,7 @@
         <v>2018</v>
       </c>
       <c r="C979" t="n">
-        <v>133.04</v>
+        <v>133.040480361667</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -32749,7 +32737,7 @@
         <v>2019</v>
       </c>
       <c r="C980" t="n">
-        <v>135.756</v>
+        <v>135.755672834643</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -32782,7 +32770,7 @@
         <v>2020</v>
       </c>
       <c r="C981" t="n">
-        <v>133.633</v>
+        <v>133.632904273198</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -32815,7 +32803,7 @@
         <v>2021</v>
       </c>
       <c r="C982" t="n">
-        <v>135.268</v>
+        <v>135.268252737261</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -32848,7 +32836,7 @@
         <v>2022</v>
       </c>
       <c r="C983" t="n">
-        <v>136.029</v>
+        <v>136.029289645522</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -32881,7 +32869,7 @@
         <v>2023</v>
       </c>
       <c r="C984" t="n">
-        <v>138.233</v>
+        <v>138.232946210214</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -32914,7 +32902,7 @@
         <v>2024</v>
       </c>
       <c r="C985" t="n">
-        <v>139.968</v>
+        <v>139.967676092657</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
